--- a/outputs/EH3_stc_results_2026-05-20.xlsx
+++ b/outputs/EH3_stc_results_2026-05-20.xlsx
@@ -604,7 +604,7 @@
         <v>121.2121212121212</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P2" t="n">
         <v>120</v>
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>131.3119461154526</v>
+        <v>131.2425654400113</v>
       </c>
       <c r="L3" t="n">
         <v>84.38387755102042</v>
@@ -678,13 +678,13 @@
         <v>14.1452</v>
       </c>
       <c r="N3" t="n">
-        <v>102.9280685644322</v>
+        <v>102.8586878889909</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P3" t="n">
-        <v>221.8987878787879</v>
+        <v>221.830101010101</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
@@ -749,22 +749,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>52.99999999999998</v>
+        <v>53</v>
       </c>
       <c r="M4" t="n">
         <v>14.1452</v>
       </c>
       <c r="N4" t="n">
-        <v>2.131628207280301e-14</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>30.75620000000003</v>
+        <v>30.75620000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>190.8319191919192</v>
+        <v>190.7632323232323</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -802,7 +802,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E5" t="n">
         <v>38.078</v>
@@ -826,22 +826,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>54.50000000000004</v>
+        <v>54.5</v>
       </c>
       <c r="M5" t="n">
         <v>15.2312</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.512019772889243e-14</v>
+        <v>2.512019772889243e-14</v>
       </c>
       <c r="O5" t="n">
-        <v>30.37219999999997</v>
+        <v>30.30420000000001</v>
       </c>
       <c r="P5" t="n">
         <v>160.1529292929293</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -903,22 +903,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>61.99999999999999</v>
+        <v>62</v>
       </c>
       <c r="M6" t="n">
         <v>15.2312</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22.95420000000002</v>
+        <v>22.95420000000001</v>
       </c>
       <c r="P6" t="n">
         <v>136.9668686868687</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>120</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E8" t="n">
         <v>48.821</v>
@@ -1054,22 +1054,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>234.1966661461035</v>
+        <v>254.7458941507427</v>
       </c>
       <c r="L8" t="n">
-        <v>96.52489795918368</v>
+        <v>105.7616326530612</v>
       </c>
       <c r="M8" t="n">
         <v>19.5284</v>
       </c>
       <c r="N8" t="n">
-        <v>216.6717681869198</v>
+        <v>227.9842614976815</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="P8" t="n">
-        <v>334.5050505050506</v>
+        <v>345.7044188827047</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1146,10 +1146,10 @@
         <v>35.04640000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>299.1046464646465</v>
+        <v>310.3040148423006</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -1220,13 +1220,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>85.73739999999999</v>
+        <v>85.73740000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>212.5012121212121</v>
+        <v>223.7005804988663</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E11" t="n">
         <v>45.383</v>
@@ -1282,22 +1282,22 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>53.50000000000002</v>
+        <v>54.99757684298202</v>
       </c>
       <c r="M11" t="n">
         <v>18.1532</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.153159805333637e-14</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>91.57619999999999</v>
+        <v>102.6635746938776</v>
       </c>
       <c r="P11" t="n">
         <v>120</v>
@@ -1359,7 +1359,7 @@
         <v>34</v>
       </c>
       <c r="J12" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1368,16 +1368,16 @@
         <v>159.7563265306122</v>
       </c>
       <c r="M12" t="n">
-        <v>18.1532</v>
+        <v>18.15319999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>154.1134578104275</v>
+        <v>160.1131517192124</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="P12" t="n">
-        <v>272.5723232323232</v>
+        <v>278.5120202020203</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>45.383</v>
+        <v>45.38299999999998</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1454,7 +1454,7 @@
         <v>125.567</v>
       </c>
       <c r="P13" t="n">
-        <v>145.7369696969697</v>
+        <v>151.6766666666667</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1466,7 +1466,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E14" t="n">
         <v>56.911</v>
@@ -1507,31 +1507,31 @@
         <v>35</v>
       </c>
       <c r="H14" t="n">
-        <v>1.499999999999318</v>
+        <v>0.4797979797979688</v>
       </c>
       <c r="I14" t="n">
-        <v>33.50000000000068</v>
+        <v>34.52020202020203</v>
       </c>
       <c r="J14" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>165.1544897959184</v>
+        <v>162.2453061224489</v>
       </c>
       <c r="M14" t="n">
         <v>22.7644</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000000000000028</v>
+        <v>1.000000000000018</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.748001908832066e-14</v>
+        <v>3.671063453225542e-14</v>
       </c>
       <c r="P14" t="n">
-        <v>146.7269696969698</v>
+        <v>152.6666666666667</v>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1584,31 +1584,31 @@
         <v>54.5</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>5.520408163265332</v>
       </c>
       <c r="I15" t="n">
-        <v>52.5</v>
+        <v>48.97959183673467</v>
       </c>
       <c r="J15" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>162.245306122449</v>
+        <v>162.2453061224489</v>
       </c>
       <c r="M15" t="n">
         <v>22.7644</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>1.000000000000059</v>
       </c>
       <c r="O15" t="n">
-        <v>4.726219415829291e-14</v>
+        <v>2.033373469600974e-14</v>
       </c>
       <c r="P15" t="n">
-        <v>147.7169696969698</v>
+        <v>153.6566666666668</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -1667,7 +1667,7 @@
         <v>107</v>
       </c>
       <c r="J16" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1679,13 +1679,13 @@
         <v>21.4324</v>
       </c>
       <c r="N16" t="n">
-        <v>107.7766059791858</v>
+        <v>164.4880666071145</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>254.4158096163637</v>
+        <v>316.4998526077101</v>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -1726,7 +1726,7 @@
         <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E17" t="n">
         <v>41.57</v>
@@ -1744,25 +1744,25 @@
         <v>163</v>
       </c>
       <c r="J17" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>142.2724489795919</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M17" t="n">
         <v>16.628</v>
       </c>
       <c r="N17" t="n">
-        <v>573.0051020408164</v>
+        <v>586.4999999999997</v>
       </c>
       <c r="O17" t="n">
-        <v>5.627498467219993e-14</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>821.6908606367718</v>
+        <v>897.1348526077097</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1815,31 +1815,31 @@
         <v>219.5</v>
       </c>
       <c r="H18" t="n">
-        <v>64.52040816325902</v>
+        <v>2.020408163265188</v>
       </c>
       <c r="I18" t="n">
-        <v>154.979591836741</v>
+        <v>217.4795918367348</v>
       </c>
       <c r="J18" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>160.2775510204082</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M18" t="n">
         <v>16.628</v>
       </c>
       <c r="N18" t="n">
-        <v>0.9999999999939746</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>5.066946862086752e-14</v>
+        <v>2.160871481748927e-13</v>
       </c>
       <c r="P18" t="n">
-        <v>822.6808606367658</v>
+        <v>898.1248526077095</v>
       </c>
       <c r="Q18" t="n">
         <v>0.9999999999999998</v>
@@ -1860,7 +1860,7 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         <v>285.5</v>
       </c>
       <c r="H19" t="n">
-        <v>57.47969594939298</v>
+        <v>42.50000000000011</v>
       </c>
       <c r="I19" t="n">
-        <v>228.020304050607</v>
+        <v>242.9999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>19.5068</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000000000000009</v>
+        <v>1.000000000000006</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>823.6708606367658</v>
+        <v>899.1148526077095</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1957,7 +1957,7 @@
         <v>19</v>
       </c>
       <c r="D20" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E20" t="n">
         <v>43.091</v>
@@ -1969,10 +1969,10 @@
         <v>320</v>
       </c>
       <c r="H20" t="n">
-        <v>141.8769387755101</v>
+        <v>138.6340816326531</v>
       </c>
       <c r="I20" t="n">
-        <v>178.1230612244899</v>
+        <v>181.3659183673469</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1981,22 +1981,22 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>141.8769387755102</v>
+        <v>137.6340816326531</v>
       </c>
       <c r="M20" t="n">
         <v>17.2364</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>1.000000000000024</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P20" t="n">
-        <v>822.6607596266648</v>
+        <v>900.1048526077095</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2046,10 +2046,10 @@
         <v>317.5</v>
       </c>
       <c r="H21" t="n">
-        <v>136.6136734693877</v>
+        <v>138.6340816326531</v>
       </c>
       <c r="I21" t="n">
-        <v>180.8863265306123</v>
+        <v>178.8659183673469</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2058,22 +2058,22 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>136.6136734693877</v>
+        <v>137.6340816326531</v>
       </c>
       <c r="M21" t="n">
         <v>17.2364</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.87087974044485e-14</v>
+        <v>1.000000000000024</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P21" t="n">
-        <v>821.6506586165638</v>
+        <v>901.0948526077095</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -2144,10 +2144,10 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0.9999999999999929</v>
       </c>
       <c r="P22" t="n">
-        <v>820.6405576064628</v>
+        <v>900.0847515976086</v>
       </c>
       <c r="Q22" t="n">
         <v>-0</v>
@@ -2188,7 +2188,7 @@
         <v>22</v>
       </c>
       <c r="D23" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E23" t="n">
         <v>40.775</v>
@@ -2200,10 +2200,10 @@
         <v>280</v>
       </c>
       <c r="H23" t="n">
-        <v>137.9530612244898</v>
+        <v>127.9112244897959</v>
       </c>
       <c r="I23" t="n">
-        <v>142.0469387755102</v>
+        <v>152.0887755102041</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2212,19 +2212,19 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>137.9530612244898</v>
+        <v>127.9112244897959</v>
       </c>
       <c r="M23" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="P23" t="n">
-        <v>819.6304565963618</v>
+        <v>899.0746505875076</v>
       </c>
       <c r="Q23" t="n">
         <v>-0</v>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2277,10 +2277,10 @@
         <v>270.5</v>
       </c>
       <c r="H24" t="n">
-        <v>167.4947232895954</v>
+        <v>127.9112244897959</v>
       </c>
       <c r="I24" t="n">
-        <v>103.0052767104046</v>
+        <v>142.5887755102041</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>128.9316326530612</v>
+        <v>127.9112244897959</v>
       </c>
       <c r="M24" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>38.56309063653416</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>857.8079163265306</v>
+        <v>898.0645495774065</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>262</v>
       </c>
       <c r="H25" t="n">
-        <v>262</v>
+        <v>221.3367340900245</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>40.66326590997554</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
         <v>13.8592</v>
       </c>
       <c r="N25" t="n">
-        <v>143.6283673469388</v>
+        <v>102.9651014369632</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>121.2121212121212</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P26" t="n">
         <v>120</v>
@@ -2464,7 +2464,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2517,19 +2517,19 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>69.40418160162751</v>
+        <v>69.4041816016275</v>
       </c>
       <c r="L27" t="n">
-        <v>84.38387755102042</v>
+        <v>84.38387755102039</v>
       </c>
       <c r="M27" t="n">
         <v>14.1452</v>
       </c>
       <c r="N27" t="n">
-        <v>1.020304050607095</v>
+        <v>1.020304050607109</v>
       </c>
       <c r="O27" t="n">
-        <v>1.340927369142264e-14</v>
+        <v>2.725819570059684e-14</v>
       </c>
       <c r="P27" t="n">
         <v>121.010101010101</v>
@@ -2650,7 +2650,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E29" t="n">
         <v>38.078</v>
@@ -2671,10 +2671,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>79.99204081632656</v>
+        <v>79.92265306122449</v>
       </c>
       <c r="L29" t="n">
-        <v>85.49204081632655</v>
+        <v>85.42265306122448</v>
       </c>
       <c r="M29" t="n">
         <v>15.2312</v>
@@ -2683,13 +2683,13 @@
         <v>1.000000000000014</v>
       </c>
       <c r="O29" t="n">
-        <v>-9.12270259334491e-15</v>
+        <v>1.901478974275505e-14</v>
       </c>
       <c r="P29" t="n">
         <v>120.99</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.000000000000014</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2748,22 +2748,22 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>615.2264996074954</v>
+        <v>635.7747851843525</v>
       </c>
       <c r="L30" t="n">
-        <v>85.42265306122449</v>
+        <v>85.42265306122451</v>
       </c>
       <c r="M30" t="n">
         <v>15.2312</v>
       </c>
       <c r="N30" t="n">
-        <v>537.3038465462708</v>
+        <v>557.8521321231279</v>
       </c>
       <c r="O30" t="n">
-        <v>1.406874616804998e-14</v>
+        <v>9.848122317634988e-14</v>
       </c>
       <c r="P30" t="n">
-        <v>652.9208080808081</v>
+        <v>673.2636108018966</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
@@ -2840,10 +2840,10 @@
         <v>80.98719999999999</v>
       </c>
       <c r="P31" t="n">
-        <v>571.1155555555556</v>
+        <v>591.458358276644</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2881,7 +2881,7 @@
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E32" t="n">
         <v>48.821</v>
@@ -2914,13 +2914,13 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>81.36440000000007</v>
+        <v>90.41640000000004</v>
       </c>
       <c r="P32" t="n">
-        <v>488.9292929292929</v>
+        <v>500.128661306947</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2988,16 +2988,16 @@
         <v>19.5284</v>
       </c>
       <c r="N33" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>88.4564</v>
       </c>
       <c r="P33" t="n">
-        <v>399.5793939393939</v>
+        <v>410.7787623170481</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -3059,19 +3059,19 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>12.50000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="M34" t="n">
         <v>24.5644</v>
       </c>
       <c r="N34" t="n">
-        <v>1.14835189617794e-13</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>138.1674</v>
       </c>
       <c r="P34" t="n">
-        <v>260.0163636363637</v>
+        <v>271.2157320140178</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
         <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E35" t="n">
         <v>45.383</v>
@@ -3130,28 +3130,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>5.499999999999948</v>
+        <v>6.997576842982035</v>
       </c>
       <c r="M35" t="n">
         <v>18.1532</v>
       </c>
       <c r="N35" t="n">
-        <v>-2.153159805333637e-14</v>
+        <v>3.319454699889357e-14</v>
       </c>
       <c r="O35" t="n">
-        <v>138.6162</v>
+        <v>149.7035746938776</v>
       </c>
       <c r="P35" t="n">
         <v>120</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -3207,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3219,13 +3219,13 @@
         <v>18.1532</v>
       </c>
       <c r="N36" t="n">
-        <v>158.1134578104275</v>
+        <v>164.1131517192124</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P36" t="n">
-        <v>276.5323232323232</v>
+        <v>282.4720202020202</v>
       </c>
       <c r="Q36" t="n">
         <v>1</v>
@@ -3290,19 +3290,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>3.999999999999958</v>
+        <v>4</v>
       </c>
       <c r="M37" t="n">
         <v>19.8</v>
       </c>
       <c r="N37" t="n">
-        <v>6.908054375445418e-14</v>
+        <v>-2.646592260722596e-14</v>
       </c>
       <c r="O37" t="n">
         <v>154.967</v>
       </c>
       <c r="P37" t="n">
-        <v>120</v>
+        <v>125.939696969697</v>
       </c>
       <c r="Q37" t="n">
         <v>-0</v>
@@ -3343,7 +3343,7 @@
         <v>13</v>
       </c>
       <c r="D38" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E38" t="n">
         <v>56.911</v>
@@ -3361,25 +3361,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>165.1544897959184</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M38" t="n">
         <v>22.7644</v>
       </c>
       <c r="N38" t="n">
-        <v>3.500000000000735</v>
+        <v>4.520202020202022</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P38" t="n">
-        <v>123.4650000000007</v>
+        <v>130.414696969697</v>
       </c>
       <c r="Q38" t="n">
         <v>1</v>
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T38" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3438,28 +3438,28 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>162.245306122449</v>
+        <v>161.2248979591837</v>
       </c>
       <c r="M39" t="n">
         <v>22.7644</v>
       </c>
       <c r="N39" t="n">
-        <v>2.499999999999965</v>
+        <v>6.95291187138987e-15</v>
       </c>
       <c r="O39" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>1.000000000000007</v>
       </c>
       <c r="P39" t="n">
-        <v>125.9400000000007</v>
+        <v>129.404595959596</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -3515,25 +3515,25 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>147.1748979591889</v>
+        <v>147.1748979591837</v>
       </c>
       <c r="M40" t="n">
         <v>21.4324</v>
       </c>
       <c r="N40" t="n">
-        <v>116.7766059791805</v>
+        <v>173.4880666071145</v>
       </c>
       <c r="O40" t="n">
-        <v>-5.115907697472721e-12</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="P40" t="n">
-        <v>241.5488399193946</v>
+        <v>301.1577819006393</v>
       </c>
       <c r="Q40" t="n">
         <v>1</v>
@@ -3574,7 +3574,7 @@
         <v>16</v>
       </c>
       <c r="D41" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E41" t="n">
         <v>41.57</v>
@@ -3592,28 +3592,28 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>142.2724489795919</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M41" t="n">
         <v>16.628</v>
       </c>
       <c r="N41" t="n">
-        <v>584.0051020408163</v>
+        <v>597.4999999999998</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P41" t="n">
-        <v>819.7138909398027</v>
+        <v>892.682781900639</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -3669,28 +3669,28 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>107.7571428571428</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M42" t="n">
         <v>16.628</v>
       </c>
       <c r="N42" t="n">
-        <v>3.157967714489334e-13</v>
+        <v>9.979591836734722</v>
       </c>
       <c r="O42" t="n">
-        <v>51.47000000000006</v>
+        <v>3.907985046680551e-14</v>
       </c>
       <c r="P42" t="n">
-        <v>767.723991949904</v>
+        <v>902.5625778190064</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -3746,28 +3746,28 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>109.2343856832601</v>
+        <v>124.2140816326531</v>
       </c>
       <c r="M43" t="n">
         <v>19.5068</v>
       </c>
       <c r="N43" t="n">
-        <v>-7.894919286223335e-14</v>
+        <v>-9.33035915644576e-14</v>
       </c>
       <c r="O43" t="n">
-        <v>35.26010203040505</v>
+        <v>20.57999999999998</v>
       </c>
       <c r="P43" t="n">
-        <v>732.1077272727271</v>
+        <v>881.7746990311275</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3805,7 +3805,7 @@
         <v>19</v>
       </c>
       <c r="D44" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E44" t="n">
         <v>43.091</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>112.5993999999999</v>
+        <v>107.4414000000001</v>
       </c>
       <c r="P44" t="n">
-        <v>618.3709595959594</v>
+        <v>773.2480323644608</v>
       </c>
       <c r="Q44" t="n">
         <v>-0</v>
@@ -3906,19 +3906,19 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>34.5</v>
+        <v>34.50000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>17.2364</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-1.14835189617794e-13</v>
       </c>
       <c r="O45" t="n">
         <v>101.0714</v>
       </c>
       <c r="P45" t="n">
-        <v>516.2786363636362</v>
+        <v>671.1557091321374</v>
       </c>
       <c r="Q45" t="n">
         <v>-0</v>
@@ -3995,7 +3995,7 @@
         <v>97.06400000000002</v>
       </c>
       <c r="P46" t="n">
-        <v>418.2341919191917</v>
+        <v>573.1112646876929</v>
       </c>
       <c r="Q46" t="n">
         <v>-0</v>
@@ -4036,7 +4036,7 @@
         <v>22</v>
       </c>
       <c r="D47" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E47" t="n">
         <v>40.775</v>
@@ -4069,10 +4069,10 @@
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O47" t="n">
-        <v>92.584</v>
+        <v>82.74299999999997</v>
       </c>
       <c r="P47" t="n">
-        <v>324.7149999999998</v>
+        <v>489.5324768089051</v>
       </c>
       <c r="Q47" t="n">
         <v>-0</v>
@@ -4146,10 +4146,10 @@
         <v>-7.105427357601002e-15</v>
       </c>
       <c r="O48" t="n">
-        <v>85.19299999999998</v>
+        <v>85.19299999999996</v>
       </c>
       <c r="P48" t="n">
-        <v>238.6614646464645</v>
+        <v>403.4789414553697</v>
       </c>
       <c r="Q48" t="n">
         <v>-0</v>
@@ -4226,7 +4226,7 @@
         <v>82.6842</v>
       </c>
       <c r="P49" t="n">
-        <v>155.1420707070705</v>
+        <v>319.9595475159758</v>
       </c>
       <c r="Q49" t="n">
         <v>-0</v>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>45.59599876314162</v>
+        <v>45.59599876314163</v>
       </c>
       <c r="L50" t="n">
         <v>84.38387755102042</v>
@@ -4300,7 +4300,7 @@
         <v>121.2121212121212</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P50" t="n">
         <v>120</v>
@@ -4356,10 +4356,10 @@
         <v>154</v>
       </c>
       <c r="H51" t="n">
-        <v>133.5211021782451</v>
+        <v>154</v>
       </c>
       <c r="I51" t="n">
-        <v>20.47889782175494</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4374,13 +4374,13 @@
         <v>14.1452</v>
       </c>
       <c r="N51" t="n">
-        <v>49.13722462722464</v>
+        <v>69.61612244897958</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P51" t="n">
-        <v>168.6458523809524</v>
+        <v>188.9199612244898</v>
       </c>
       <c r="Q51" t="n">
         <v>1</v>
@@ -4389,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -4454,10 +4454,10 @@
         <v>53.61612244897958</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P52" t="n">
-        <v>221.7258136054422</v>
+        <v>241.9999224489796</v>
       </c>
       <c r="Q52" t="n">
         <v>1</v>
@@ -4466,7 +4466,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T52" t="n">
         <v>0</v>
@@ -4498,7 +4498,7 @@
         <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E53" t="n">
         <v>38.078</v>
@@ -4522,19 +4522,19 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>85.49204081632654</v>
+        <v>85.42265306122449</v>
       </c>
       <c r="M53" t="n">
         <v>15.2312</v>
       </c>
       <c r="N53" t="n">
-        <v>42.00795918367346</v>
+        <v>42.07734693877551</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>263.313693197279</v>
+        <v>283.6564959183674</v>
       </c>
       <c r="Q53" t="n">
         <v>1</v>
@@ -4543,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T53" t="n">
         <v>0</v>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>298.5352666666667</v>
+        <v>318.8780693877551</v>
       </c>
       <c r="Q54" t="n">
         <v>1</v>
@@ -4620,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T54" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>315.2266666666667</v>
+        <v>335.5694693877551</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T55" t="n">
         <v>0</v>
@@ -4729,7 +4729,7 @@
         <v>7</v>
       </c>
       <c r="D56" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E56" t="n">
         <v>48.821</v>
@@ -4762,10 +4762,10 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1.004400000000004</v>
+        <v>10.05639999999999</v>
       </c>
       <c r="P56" t="n">
-        <v>314.2121212121212</v>
+        <v>325.4114895897753</v>
       </c>
       <c r="Q56" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T56" t="n">
         <v>0</v>
@@ -4839,10 +4839,10 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>22.79640000000001</v>
+        <v>22.7964</v>
       </c>
       <c r="P57" t="n">
-        <v>291.1854545454545</v>
+        <v>302.3848229231087</v>
       </c>
       <c r="Q57" t="n">
         <v>0</v>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T57" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>74.95739999999999</v>
       </c>
       <c r="P58" t="n">
-        <v>215.4709090909091</v>
+        <v>226.6702774685632</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
@@ -4928,7 +4928,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
@@ -4960,7 +4960,7 @@
         <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E59" t="n">
         <v>45.383</v>
@@ -4978,34 +4978,34 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>50.5</v>
+        <v>51.997576842982</v>
       </c>
       <c r="M59" t="n">
         <v>18.1532</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>1.509903313490213e-14</v>
       </c>
       <c r="O59" t="n">
-        <v>94.5162</v>
+        <v>105.6035746938776</v>
       </c>
       <c r="P59" t="n">
         <v>120</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T59" t="n">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>32</v>
       </c>
       <c r="J60" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -5064,16 +5064,16 @@
         <v>159.7563265306123</v>
       </c>
       <c r="M60" t="n">
-        <v>18.1532</v>
+        <v>18.15319999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>154.1134578104275</v>
+        <v>160.1131517192123</v>
       </c>
       <c r="O60" t="n">
-        <v>-5.627498467219993e-14</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>272.5723232323232</v>
+        <v>278.5120202020202</v>
       </c>
       <c r="Q60" t="n">
         <v>1</v>
@@ -5085,16 +5085,16 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.368475785867e-14</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>2.131628207280301e-14</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>45.383</v>
+        <v>45.38299999999998</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -5150,7 +5150,7 @@
         <v>95.67699999999996</v>
       </c>
       <c r="P61" t="n">
-        <v>175.9288888888889</v>
+        <v>181.8685858585859</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
@@ -5191,7 +5191,7 @@
         <v>13</v>
       </c>
       <c r="D62" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E62" t="n">
         <v>56.911</v>
@@ -5203,31 +5203,31 @@
         <v>78.5</v>
       </c>
       <c r="H62" t="n">
-        <v>1.499999999999318</v>
+        <v>0.4797979797980558</v>
       </c>
       <c r="I62" t="n">
-        <v>77.00000000000068</v>
+        <v>78.02020202020195</v>
       </c>
       <c r="J62" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>165.1544897959184</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M62" t="n">
         <v>22.7644</v>
       </c>
       <c r="N62" t="n">
-        <v>1.000000000000028</v>
+        <v>1.00000000000002</v>
       </c>
       <c r="O62" t="n">
-        <v>-9.342526752220691e-15</v>
+        <v>-1.780575686893826e-14</v>
       </c>
       <c r="P62" t="n">
-        <v>176.918888888889</v>
+        <v>182.8585858585859</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5280,13 +5280,13 @@
         <v>72.5</v>
       </c>
       <c r="H63" t="n">
-        <v>32.61855986186715</v>
+        <v>5.52040816326533</v>
       </c>
       <c r="I63" t="n">
-        <v>39.88144013813285</v>
+        <v>66.97959183673467</v>
       </c>
       <c r="J63" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -5298,16 +5298,16 @@
         <v>22.7644</v>
       </c>
       <c r="N63" t="n">
-        <v>31.61855986186715</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>5.979217121421242e-14</v>
+        <v>-3.715028285000699e-14</v>
       </c>
       <c r="P63" t="n">
-        <v>208.2212631521374</v>
+        <v>183.848585858586</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -5357,13 +5357,13 @@
         <v>65.5</v>
       </c>
       <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
         <v>65.5</v>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
       <c r="J64" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -5375,13 +5375,13 @@
         <v>21.4324</v>
       </c>
       <c r="N64" t="n">
-        <v>173.2766059791857</v>
+        <v>164.4880666071145</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>379.7651030715312</v>
+        <v>346.6917717996293</v>
       </c>
       <c r="Q64" t="n">
         <v>1</v>
@@ -5422,7 +5422,7 @@
         <v>16</v>
       </c>
       <c r="D65" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E65" t="n">
         <v>41.57</v>
@@ -5434,31 +5434,31 @@
         <v>69.5</v>
       </c>
       <c r="H65" t="n">
-        <v>26.99489795918362</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>42.50510204081638</v>
+        <v>69.5</v>
       </c>
       <c r="J65" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>142.2724489795919</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M65" t="n">
         <v>16.628</v>
       </c>
       <c r="N65" t="n">
-        <v>599.9999999999999</v>
+        <v>586.4999999999997</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P65" t="n">
-        <v>973.7651030715311</v>
+        <v>927.3267717996289</v>
       </c>
       <c r="Q65" t="n">
         <v>1</v>
@@ -5479,7 +5479,7 @@
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -5511,34 +5511,34 @@
         <v>72</v>
       </c>
       <c r="H66" t="n">
-        <v>72</v>
+        <v>41.42770937576154</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>30.57229062423846</v>
       </c>
       <c r="J66" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>160.2775510204082</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M66" t="n">
         <v>16.628</v>
       </c>
       <c r="N66" t="n">
-        <v>8.479591836735128</v>
+        <v>40.40730121249625</v>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P66" t="n">
-        <v>982.1598989898989</v>
+        <v>967.3300000000002</v>
       </c>
       <c r="Q66" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
@@ -5556,7 +5556,7 @@
         <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X66" t="n">
         <v>0</v>
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>19.5068</v>
       </c>
       <c r="N67" t="n">
-        <v>18.02030405060715</v>
+        <v>32.99999999999984</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>19</v>
       </c>
       <c r="D68" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E68" t="n">
         <v>43.091</v>
@@ -5677,19 +5677,19 @@
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>81.49999999999994</v>
+        <v>81.50000000000001</v>
       </c>
       <c r="M68" t="n">
         <v>17.2364</v>
       </c>
       <c r="N68" t="n">
-        <v>1.435439870222425e-14</v>
+        <v>-1.004807909155697e-13</v>
       </c>
       <c r="O68" t="n">
-        <v>60.16940000000005</v>
+        <v>55.01139999999998</v>
       </c>
       <c r="P68" t="n">
-        <v>939.2228282828282</v>
+        <v>944.4329292929292</v>
       </c>
       <c r="Q68" t="n">
         <v>-0</v>
@@ -5754,19 +5754,19 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>87.50000000000004</v>
+        <v>87.50000000000006</v>
       </c>
       <c r="M69" t="n">
         <v>17.2364</v>
       </c>
       <c r="N69" t="n">
-        <v>2.870879740444849e-14</v>
+        <v>1.435439870222425e-13</v>
       </c>
       <c r="O69" t="n">
         <v>49.13139999999994</v>
       </c>
       <c r="P69" t="n">
-        <v>889.5951515151515</v>
+        <v>894.8052525252526</v>
       </c>
       <c r="Q69" t="n">
         <v>-0</v>
@@ -5793,7 +5793,7 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -5840,10 +5840,10 @@
         <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>53.94400000000002</v>
+        <v>53.94400000000001</v>
       </c>
       <c r="P70" t="n">
-        <v>835.1062626262626</v>
+        <v>840.3163636363637</v>
       </c>
       <c r="Q70" t="n">
         <v>-0</v>
@@ -5884,7 +5884,7 @@
         <v>22</v>
       </c>
       <c r="D71" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E71" t="n">
         <v>40.775</v>
@@ -5911,16 +5911,16 @@
         <v>79.50000000000001</v>
       </c>
       <c r="M71" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N71" t="n">
         <v>-1.4210854715202e-14</v>
       </c>
       <c r="O71" t="n">
-        <v>58.28399999999998</v>
+        <v>48.44299999999998</v>
       </c>
       <c r="P71" t="n">
-        <v>776.2335353535353</v>
+        <v>791.3840404040404</v>
       </c>
       <c r="Q71" t="n">
         <v>-0</v>
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
@@ -5985,19 +5985,19 @@
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>71.49999999999997</v>
+        <v>71.5</v>
       </c>
       <c r="M72" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N72" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>56.28300000000004</v>
+        <v>56.283</v>
       </c>
       <c r="P72" t="n">
-        <v>719.3820202020202</v>
+        <v>734.5325252525253</v>
       </c>
       <c r="Q72" t="n">
         <v>-0</v>
@@ -6018,7 +6018,7 @@
         <v>0</v>
       </c>
       <c r="W72" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X72" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
         <v>59.6542</v>
       </c>
       <c r="P73" t="n">
-        <v>659.1252525252524</v>
+        <v>674.2757575757576</v>
       </c>
       <c r="Q73" t="n">
         <v>-0</v>
@@ -6101,7 +6101,7 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.9999999999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -6145,10 +6145,10 @@
         <v>14.1452</v>
       </c>
       <c r="N74" t="n">
-        <v>135.5945311702888</v>
+        <v>135.5945311702887</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P74" t="n">
         <v>134.2385858585859</v>
@@ -6160,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T74" t="n">
         <v>0</v>
@@ -6225,13 +6225,13 @@
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>14.09620000000002</v>
+        <v>14.09619999999999</v>
       </c>
       <c r="P75" t="n">
         <v>120</v>
       </c>
       <c r="Q75" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -6281,10 +6281,10 @@
         <v>104.5</v>
       </c>
       <c r="H76" t="n">
-        <v>85.38387755102043</v>
+        <v>85.3838775510204</v>
       </c>
       <c r="I76" t="n">
-        <v>19.11612244897957</v>
+        <v>19.1161224489796</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6293,16 +6293,16 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>84.38387755102045</v>
+        <v>84.3838775510204</v>
       </c>
       <c r="M76" t="n">
         <v>14.1452</v>
       </c>
       <c r="N76" t="n">
-        <v>0.9999999999999858</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
-        <v>-2.297162460251911e-14</v>
+        <v>5.055955654142963e-15</v>
       </c>
       <c r="P76" t="n">
         <v>120.99</v>
@@ -6346,7 +6346,7 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E77" t="n">
         <v>38.078</v>
@@ -6358,10 +6358,10 @@
         <v>143</v>
       </c>
       <c r="H77" t="n">
-        <v>86.49204081632654</v>
+        <v>86.42265306122448</v>
       </c>
       <c r="I77" t="n">
-        <v>56.50795918367346</v>
+        <v>56.57734693877552</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6370,16 +6370,16 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>85.49204081632654</v>
+        <v>85.42265306122448</v>
       </c>
       <c r="M77" t="n">
-        <v>15.2312</v>
+        <v>15.23119999999999</v>
       </c>
       <c r="N77" t="n">
         <v>1</v>
       </c>
       <c r="O77" t="n">
-        <v>-2.3081536681957e-14</v>
+        <v>-9.01279051390702e-15</v>
       </c>
       <c r="P77" t="n">
         <v>121.98</v>
@@ -6403,7 +6403,7 @@
         <v>0</v>
       </c>
       <c r="W77" t="n">
-        <v>38.078</v>
+        <v>38.07799999999997</v>
       </c>
       <c r="X77" t="n">
         <v>0</v>
@@ -6435,10 +6435,10 @@
         <v>160</v>
       </c>
       <c r="H78" t="n">
-        <v>86.42265306122449</v>
+        <v>86.42265306122448</v>
       </c>
       <c r="I78" t="n">
-        <v>73.57734693877551</v>
+        <v>73.57734693877552</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -6447,16 +6447,16 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>85.42265306122449</v>
+        <v>85.42265306122448</v>
       </c>
       <c r="M78" t="n">
-        <v>15.2312</v>
+        <v>15.23119999999999</v>
       </c>
       <c r="N78" t="n">
         <v>1</v>
       </c>
       <c r="O78" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P78" t="n">
         <v>122.97</v>
@@ -6480,7 +6480,7 @@
         <v>0</v>
       </c>
       <c r="W78" t="n">
-        <v>38.078</v>
+        <v>38.07799999999997</v>
       </c>
       <c r="X78" t="n">
         <v>0</v>
@@ -6512,10 +6512,10 @@
         <v>156.5</v>
       </c>
       <c r="H79" t="n">
-        <v>93.14</v>
+        <v>93.13999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>63.36</v>
+        <v>63.36000000000001</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -6524,16 +6524,16 @@
         <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>92.14</v>
+        <v>92.13999999999999</v>
       </c>
       <c r="M79" t="n">
-        <v>15.2312</v>
+        <v>15.23119999999999</v>
       </c>
       <c r="N79" t="n">
         <v>1</v>
       </c>
       <c r="O79" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P79" t="n">
         <v>123.96</v>
@@ -6557,7 +6557,7 @@
         <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>38.078</v>
+        <v>38.07799999999997</v>
       </c>
       <c r="X79" t="n">
         <v>0</v>
@@ -6577,7 +6577,7 @@
         <v>7</v>
       </c>
       <c r="D80" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E80" t="n">
         <v>48.821</v>
@@ -6589,10 +6589,10 @@
         <v>139</v>
       </c>
       <c r="H80" t="n">
-        <v>97.52489795918368</v>
+        <v>106.7660208350252</v>
       </c>
       <c r="I80" t="n">
-        <v>41.47510204081632</v>
+        <v>32.23397916497484</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -6601,19 +6601,19 @@
         <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>96.52489795918368</v>
+        <v>105.7616326530612</v>
       </c>
       <c r="M80" t="n">
         <v>19.5284</v>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>1.004388181963932</v>
       </c>
       <c r="O80" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="P80" t="n">
-        <v>124.95</v>
+        <v>124.9543443001443</v>
       </c>
       <c r="Q80" t="n">
         <v>1</v>
@@ -6666,10 +6666,10 @@
         <v>131.5</v>
       </c>
       <c r="H81" t="n">
-        <v>120.1918948712023</v>
+        <v>131.5</v>
       </c>
       <c r="I81" t="n">
-        <v>11.30810512879775</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -6684,13 +6684,13 @@
         <v>19.5284</v>
       </c>
       <c r="N81" t="n">
-        <v>14.43026221814102</v>
+        <v>25.73836734693877</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="P81" t="n">
-        <v>139.2359595959596</v>
+        <v>150.4353279736137</v>
       </c>
       <c r="Q81" t="n">
         <v>1</v>
@@ -6764,10 +6764,10 @@
         <v>0</v>
       </c>
       <c r="O82" t="n">
-        <v>11.7474</v>
+        <v>11.74740000000001</v>
       </c>
       <c r="P82" t="n">
-        <v>127.369898989899</v>
+        <v>138.5692673675531</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
@@ -6808,7 +6808,7 @@
         <v>10</v>
       </c>
       <c r="D83" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E83" t="n">
         <v>45.383</v>
@@ -6826,22 +6826,22 @@
         <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>139.5</v>
+        <v>140.997576842982</v>
       </c>
       <c r="M83" t="n">
-        <v>18.1532</v>
+        <v>18.15319999999999</v>
       </c>
       <c r="N83" t="n">
-        <v>-1.435439870222425e-14</v>
+        <v>2.512019772889244e-14</v>
       </c>
       <c r="O83" t="n">
-        <v>7.296199999999999</v>
+        <v>18.38357469387759</v>
       </c>
       <c r="P83" t="n">
         <v>120</v>
@@ -6865,7 +6865,7 @@
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>45.383</v>
+        <v>45.38299999999998</v>
       </c>
       <c r="X83" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>142.5</v>
       </c>
       <c r="J84" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K84" t="n">
         <v>0</v>
@@ -6912,16 +6912,16 @@
         <v>159.7563265306122</v>
       </c>
       <c r="M84" t="n">
-        <v>18.1532</v>
+        <v>18.15319999999999</v>
       </c>
       <c r="N84" t="n">
-        <v>154.1134578104275</v>
+        <v>160.1131517192124</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="P84" t="n">
-        <v>272.5723232323232</v>
+        <v>278.5120202020203</v>
       </c>
       <c r="Q84" t="n">
         <v>1</v>
@@ -6942,7 +6942,7 @@
         <v>0</v>
       </c>
       <c r="W84" t="n">
-        <v>45.383</v>
+        <v>45.38299999999998</v>
       </c>
       <c r="X84" t="n">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         <v>19.8</v>
       </c>
       <c r="N85" t="n">
-        <v>3.229739708000455e-14</v>
+        <v>-7.177199351112124e-15</v>
       </c>
       <c r="O85" t="n">
-        <v>22.66700000000003</v>
+        <v>22.66699999999999</v>
       </c>
       <c r="P85" t="n">
-        <v>249.6763636363636</v>
+        <v>255.6160606060607</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>13</v>
       </c>
       <c r="D86" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E86" t="n">
         <v>56.911</v>
@@ -7051,31 +7051,31 @@
         <v>128</v>
       </c>
       <c r="H86" t="n">
-        <v>1.499999999999261</v>
+        <v>0.4797979797979792</v>
       </c>
       <c r="I86" t="n">
-        <v>126.5000000000007</v>
+        <v>127.520202020202</v>
       </c>
       <c r="J86" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>165.1544897959184</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M86" t="n">
         <v>22.7644</v>
       </c>
       <c r="N86" t="n">
-        <v>1.000000000000009</v>
+        <v>1.000000000000016</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P86" t="n">
-        <v>250.6663636363637</v>
+        <v>256.6060606060607</v>
       </c>
       <c r="Q86" t="n">
         <v>0.9999999999999998</v>
@@ -7128,34 +7128,34 @@
         <v>118.5</v>
       </c>
       <c r="H87" t="n">
-        <v>1.999999999999915</v>
+        <v>3.499999999999886</v>
       </c>
       <c r="I87" t="n">
-        <v>116.5000000000001</v>
+        <v>115.0000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>162.245306122449</v>
+        <v>161.2248979591836</v>
       </c>
       <c r="M87" t="n">
         <v>22.7644</v>
       </c>
       <c r="N87" t="n">
-        <v>0.9999999999999231</v>
+        <v>-6.818339383556516e-14</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>1.000000000000036</v>
       </c>
       <c r="P87" t="n">
-        <v>251.6563636363636</v>
+        <v>255.5959595959596</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.9999999999999998</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -7211,7 +7211,7 @@
         <v>132.5</v>
       </c>
       <c r="J88" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -7223,13 +7223,13 @@
         <v>21.4324</v>
       </c>
       <c r="N88" t="n">
-        <v>107.7766059791857</v>
+        <v>164.4880666071145</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>358.3552035557574</v>
+        <v>418.4391455370028</v>
       </c>
       <c r="Q88" t="n">
         <v>1</v>
@@ -7270,7 +7270,7 @@
         <v>16</v>
       </c>
       <c r="D89" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E89" t="n">
         <v>41.57</v>
@@ -7282,31 +7282,31 @@
         <v>152.5</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>0.9352065282802184</v>
       </c>
       <c r="I89" t="n">
-        <v>152.5</v>
+        <v>151.5647934717198</v>
       </c>
       <c r="J89" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>142.2724489795918</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M89" t="n">
         <v>16.628</v>
       </c>
       <c r="N89" t="n">
-        <v>573.0051020408165</v>
+        <v>587.4352065282799</v>
       </c>
       <c r="O89" t="n">
-        <v>1.125499693443999e-13</v>
+        <v>5.627498467219993e-14</v>
       </c>
       <c r="P89" t="n">
-        <v>925.6302545761656</v>
+        <v>999.9999999999999</v>
       </c>
       <c r="Q89" t="n">
         <v>1</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X89" t="n">
         <v>0</v>
@@ -7359,34 +7359,34 @@
         <v>170.5</v>
       </c>
       <c r="H90" t="n">
-        <v>64.52040816326819</v>
+        <v>-0</v>
       </c>
       <c r="I90" t="n">
-        <v>105.9795918367318</v>
+        <v>170.5</v>
       </c>
       <c r="J90" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>160.2775510204082</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="M90" t="n">
         <v>16.628</v>
       </c>
       <c r="N90" t="n">
-        <v>1.000000000003169</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
-        <v>-5.440647932175579e-14</v>
+        <v>0.9999999999999158</v>
       </c>
       <c r="P90" t="n">
-        <v>926.6202545761688</v>
+        <v>998.989898989899</v>
       </c>
       <c r="Q90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -7395,7 +7395,7 @@
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U90" t="n">
         <v>0</v>
@@ -7436,34 +7436,34 @@
         <v>174</v>
       </c>
       <c r="H91" t="n">
-        <v>107.6320794943884</v>
+        <v>40.47959183673478</v>
       </c>
       <c r="I91" t="n">
-        <v>66.36792050561161</v>
+        <v>133.5204081632652</v>
       </c>
       <c r="J91" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>145.2140816326531</v>
+        <v>144.1936734693878</v>
       </c>
       <c r="M91" t="n">
         <v>19.5068</v>
       </c>
       <c r="N91" t="n">
-        <v>51.15238354499544</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>-7.737810392427491e-14</v>
+        <v>1.000000000000028</v>
       </c>
       <c r="P91" t="n">
-        <v>977.2611142857144</v>
+        <v>997.9797979797979</v>
       </c>
       <c r="Q91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -7501,7 +7501,7 @@
         <v>19</v>
       </c>
       <c r="D92" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E92" t="n">
         <v>43.091</v>
@@ -7513,10 +7513,10 @@
         <v>162.5</v>
       </c>
       <c r="H92" t="n">
-        <v>162.5</v>
+        <v>138.6746897338672</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>23.82531026613282</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -7525,22 +7525,22 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>142.8973469387754</v>
+        <v>137.6340816326529</v>
       </c>
       <c r="M92" t="n">
         <v>17.2364</v>
       </c>
       <c r="N92" t="n">
-        <v>19.60265306122457</v>
+        <v>1.040608101214275</v>
       </c>
       <c r="O92" t="n">
-        <v>1.934452598106873e-13</v>
+        <v>6.308953359734914e-14</v>
       </c>
       <c r="P92" t="n">
-        <v>996.6677408163265</v>
+        <v>999.01</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R92" t="n">
         <v>0</v>
@@ -7549,7 +7549,7 @@
         <v>0</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U92" t="n">
         <v>0</v>
@@ -7590,10 +7590,10 @@
         <v>141</v>
       </c>
       <c r="H93" t="n">
-        <v>141</v>
+        <v>138.6340816326531</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>2.36591836734695</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -7608,10 +7608,10 @@
         <v>17.2364</v>
       </c>
       <c r="N93" t="n">
-        <v>3.36591836734697</v>
+        <v>1.00000000000002</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P93" t="n">
         <v>1000</v>
@@ -7732,7 +7732,7 @@
         <v>22</v>
       </c>
       <c r="D95" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E95" t="n">
         <v>40.775</v>
@@ -7744,10 +7744,10 @@
         <v>132</v>
       </c>
       <c r="H95" t="n">
-        <v>132</v>
+        <v>129.9316326530612</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>2.068367346938771</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -7756,22 +7756,22 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>132</v>
+        <v>128.9316326530612</v>
       </c>
       <c r="M95" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>6.834000000000003</v>
+        <v>-1.06581410364015e-14</v>
       </c>
       <c r="P95" t="n">
-        <v>978.69898989899</v>
+        <v>986.5920202020203</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X95" t="n">
         <v>0</v>
@@ -7821,10 +7821,10 @@
         <v>137</v>
       </c>
       <c r="H96" t="n">
-        <v>137</v>
+        <v>129.9316326530612</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>7.0683673469388</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -7836,16 +7836,16 @@
         <v>128.9316326530612</v>
       </c>
       <c r="M96" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N96" t="n">
-        <v>8.068367346938793</v>
+        <v>0.9999999999999983</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>-1.06581410364015e-14</v>
       </c>
       <c r="P96" t="n">
-        <v>986.6866735724594</v>
+        <v>987.5820202020203</v>
       </c>
       <c r="Q96" t="n">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="W96" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X96" t="n">
         <v>0</v>
@@ -7898,10 +7898,10 @@
         <v>139</v>
       </c>
       <c r="H97" t="n">
-        <v>131.8194371253243</v>
+        <v>130.9150465904146</v>
       </c>
       <c r="I97" t="n">
-        <v>7.180562874675672</v>
+        <v>8.084953409585438</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -7916,7 +7916,7 @@
         <v>13.8592</v>
       </c>
       <c r="N97" t="n">
-        <v>13.4478044722631</v>
+        <v>12.54341393735334</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>121.2121212121212</v>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P98" t="n">
         <v>120</v>
@@ -8008,7 +8008,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T98" t="n">
         <v>0</v>
@@ -8073,7 +8073,7 @@
         <v>0.9999999999999858</v>
       </c>
       <c r="O99" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P99" t="n">
         <v>120.99</v>
@@ -8138,19 +8138,19 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>73.88387755102039</v>
+        <v>73.88387755102042</v>
       </c>
       <c r="L100" t="n">
-        <v>84.3838775510204</v>
+        <v>84.38387755102042</v>
       </c>
       <c r="M100" t="n">
         <v>14.1452</v>
       </c>
       <c r="N100" t="n">
-        <v>0.9999999999999858</v>
+        <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P100" t="n">
         <v>121.98</v>
@@ -8194,7 +8194,7 @@
         <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E101" t="n">
         <v>38.078</v>
@@ -8215,25 +8215,25 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>72.99183673469388</v>
+        <v>72.92244897959179</v>
       </c>
       <c r="L101" t="n">
-        <v>83.49183673469388</v>
+        <v>83.42244897959181</v>
       </c>
       <c r="M101" t="n">
         <v>15.2312</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="O101" t="n">
-        <v>1.9602</v>
+        <v>1.960200000000043</v>
       </c>
       <c r="P101" t="n">
-        <v>119.9999999999999</v>
+        <v>120</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -8242,7 +8242,7 @@
         <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -8295,7 +8295,7 @@
         <v>139.5758517144232</v>
       </c>
       <c r="L102" t="n">
-        <v>85.42265306122444</v>
+        <v>85.42265306122449</v>
       </c>
       <c r="M102" t="n">
         <v>15.2312</v>
@@ -8304,10 +8304,10 @@
         <v>70.65319865319871</v>
       </c>
       <c r="O102" t="n">
-        <v>5.684341886080801e-14</v>
+        <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>189.9466666666666</v>
+        <v>189.9466666666667</v>
       </c>
       <c r="Q102" t="n">
         <v>1</v>
@@ -8316,7 +8316,7 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T102" t="n">
         <v>0</v>
@@ -8378,16 +8378,16 @@
         <v>15.2312</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="O103" t="n">
         <v>68.24720000000001</v>
       </c>
       <c r="P103" t="n">
-        <v>121.0101010101009</v>
+        <v>121.010101010101</v>
       </c>
       <c r="Q103" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
         <v>0</v>
@@ -8425,7 +8425,7 @@
         <v>7</v>
       </c>
       <c r="D104" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E104" t="n">
         <v>48.821</v>
@@ -8446,19 +8446,19 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>72.00448979591846</v>
+        <v>81.24122448979593</v>
       </c>
       <c r="L104" t="n">
-        <v>95.50448979591764</v>
+        <v>104.7412244897959</v>
       </c>
       <c r="M104" t="n">
         <v>19.5284</v>
       </c>
       <c r="N104" t="n">
-        <v>8.242295734817162e-13</v>
+        <v>1.4210854715202e-14</v>
       </c>
       <c r="O104" t="n">
-        <v>1.000000000000738</v>
+        <v>1.000000000000014</v>
       </c>
       <c r="P104" t="n">
         <v>120</v>
@@ -8470,7 +8470,7 @@
         <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T104" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0.9999999999999994</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -8523,22 +8523,22 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>363.1655200114941</v>
+        <v>374.4780133222558</v>
       </c>
       <c r="L105" t="n">
-        <v>105.7616326530612</v>
+        <v>105.7616326530613</v>
       </c>
       <c r="M105" t="n">
         <v>19.5284</v>
       </c>
       <c r="N105" t="n">
-        <v>277.9038873584329</v>
+        <v>289.2163806691946</v>
       </c>
       <c r="O105" t="n">
-        <v>5.627498467219993e-14</v>
+        <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>395.1248484848485</v>
+        <v>406.3242168625026</v>
       </c>
       <c r="Q105" t="n">
         <v>1</v>
@@ -8565,7 +8565,7 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0.9999999999999994</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -8612,10 +8612,10 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>135.7173999999999</v>
+        <v>135.7174</v>
       </c>
       <c r="P106" t="n">
-        <v>258.0365656565657</v>
+        <v>269.2359340342198</v>
       </c>
       <c r="Q106" t="n">
         <v>-0</v>
@@ -8656,7 +8656,7 @@
         <v>10</v>
       </c>
       <c r="D107" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E107" t="n">
         <v>45.383</v>
@@ -8674,22 +8674,22 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K107" t="n">
         <v>0</v>
       </c>
       <c r="L107" t="n">
-        <v>7.499999999999996</v>
+        <v>8.997576842982081</v>
       </c>
       <c r="M107" t="n">
-        <v>18.1532</v>
+        <v>18.15319999999999</v>
       </c>
       <c r="N107" t="n">
         <v>-2.870879740444849e-14</v>
       </c>
       <c r="O107" t="n">
-        <v>136.6562</v>
+        <v>147.7435746938775</v>
       </c>
       <c r="P107" t="n">
         <v>120</v>
@@ -8713,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>45.383</v>
+        <v>45.38299999999998</v>
       </c>
       <c r="X107" t="n">
         <v>0</v>
@@ -8751,25 +8751,25 @@
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K108" t="n">
-        <v>0.9998979695948923</v>
+        <v>0</v>
       </c>
       <c r="L108" t="n">
         <v>159.7563265306122</v>
       </c>
       <c r="M108" t="n">
-        <v>18.1532</v>
+        <v>18.15319999999999</v>
       </c>
       <c r="N108" t="n">
-        <v>159.1133557800225</v>
+        <v>164.1131517192124</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>2.813749233609997e-14</v>
       </c>
       <c r="P108" t="n">
-        <v>277.5222222222222</v>
+        <v>282.4720202020202</v>
       </c>
       <c r="Q108" t="n">
         <v>1</v>
@@ -8790,7 +8790,7 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>45.383</v>
+        <v>45.38299999999998</v>
       </c>
       <c r="X108" t="n">
         <v>0</v>
@@ -8834,19 +8834,19 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>2.999999999999945</v>
+        <v>3</v>
       </c>
       <c r="M109" t="n">
         <v>19.8</v>
       </c>
       <c r="N109" t="n">
-        <v>5.382899513334093e-14</v>
+        <v>-2.601734764778145e-14</v>
       </c>
       <c r="O109" t="n">
-        <v>155.9470000000001</v>
+        <v>155.947</v>
       </c>
       <c r="P109" t="n">
-        <v>120</v>
+        <v>124.949797979798</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
@@ -8887,7 +8887,7 @@
         <v>13</v>
       </c>
       <c r="D110" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E110" t="n">
         <v>56.911</v>
@@ -8905,28 +8905,28 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>165.1544897959184</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M110" t="n">
         <v>22.7644</v>
       </c>
       <c r="N110" t="n">
-        <v>2.000000000000722</v>
+        <v>3.020202020202033</v>
       </c>
       <c r="O110" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P110" t="n">
-        <v>121.9800000000007</v>
+        <v>127.939797979798</v>
       </c>
       <c r="Q110" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
         <v>0</v>
@@ -8982,28 +8982,28 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>162.245306122449</v>
+        <v>159.7248979591837</v>
       </c>
       <c r="M111" t="n">
         <v>22.7644</v>
       </c>
       <c r="N111" t="n">
-        <v>0.9999999999999805</v>
+        <v>3.588599675556062e-15</v>
       </c>
       <c r="O111" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>2.470000000000006</v>
       </c>
       <c r="P111" t="n">
-        <v>122.9700000000007</v>
+        <v>125.4448484848485</v>
       </c>
       <c r="Q111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -9059,7 +9059,7 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -9071,13 +9071,13 @@
         <v>21.4324</v>
       </c>
       <c r="N112" t="n">
-        <v>110.2766059791857</v>
+        <v>166.9880666071145</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
       </c>
       <c r="P112" t="n">
-        <v>232.1438399193946</v>
+        <v>290.7630344258918</v>
       </c>
       <c r="Q112" t="n">
         <v>1</v>
@@ -9118,7 +9118,7 @@
         <v>16</v>
       </c>
       <c r="D113" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E113" t="n">
         <v>41.57</v>
@@ -9136,28 +9136,28 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>142.2724489795918</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M113" t="n">
         <v>16.628</v>
       </c>
       <c r="N113" t="n">
-        <v>579.0051020408163</v>
+        <v>592.4999999999997</v>
       </c>
       <c r="O113" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P113" t="n">
-        <v>805.3588909398027</v>
+        <v>877.3380344258915</v>
       </c>
       <c r="Q113" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R113" t="n">
         <v>0</v>
@@ -9175,7 +9175,7 @@
         <v>0</v>
       </c>
       <c r="W113" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X113" t="n">
         <v>0</v>
@@ -9213,28 +9213,28 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>109.2571428571513</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M114" t="n">
         <v>16.628</v>
       </c>
       <c r="N114" t="n">
-        <v>-8.016931675192242e-12</v>
+        <v>11.47959183673471</v>
       </c>
       <c r="O114" t="n">
-        <v>49.99999999999176</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P114" t="n">
-        <v>754.8538404347526</v>
+        <v>888.7028303442588</v>
       </c>
       <c r="Q114" t="n">
-        <v>-7.191807262383084e-14</v>
+        <v>1</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -9252,7 +9252,7 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X114" t="n">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>105.7343856832601</v>
+        <v>120.714081632653</v>
       </c>
       <c r="M115" t="n">
         <v>19.5068</v>
@@ -9305,10 +9305,10 @@
         <v>-2.870879740444849e-14</v>
       </c>
       <c r="O115" t="n">
-        <v>38.69010203040506</v>
+        <v>24.01000000000001</v>
       </c>
       <c r="P115" t="n">
-        <v>715.7729292929292</v>
+        <v>864.4503050917335</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -9349,7 +9349,7 @@
         <v>19</v>
       </c>
       <c r="D116" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E116" t="n">
         <v>43.091</v>
@@ -9370,22 +9370,22 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>292.5303945869748</v>
+        <v>127.0471496452885</v>
       </c>
       <c r="L116" t="n">
-        <v>142.8973469387755</v>
+        <v>137.6340816326531</v>
       </c>
       <c r="M116" t="n">
         <v>17.2364</v>
       </c>
       <c r="N116" t="n">
-        <v>168.1330476481992</v>
+        <v>7.913068012635463</v>
       </c>
       <c r="O116" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P116" t="n">
-        <v>882.2246464646464</v>
+        <v>872.2842424242426</v>
       </c>
       <c r="Q116" t="n">
         <v>1</v>
@@ -9456,13 +9456,13 @@
         <v>17.2364</v>
       </c>
       <c r="N117" t="n">
-        <v>3.588599675556061e-14</v>
+        <v>-6.45947941600091e-14</v>
       </c>
       <c r="O117" t="n">
         <v>117.7314</v>
       </c>
       <c r="P117" t="n">
-        <v>763.3040404040404</v>
+        <v>753.3636363636365</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
@@ -9539,7 +9539,7 @@
         <v>123.034</v>
       </c>
       <c r="P118" t="n">
-        <v>639.0272727272727</v>
+        <v>629.0868686868688</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
@@ -9580,7 +9580,7 @@
         <v>22</v>
       </c>
       <c r="D119" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E119" t="n">
         <v>40.775</v>
@@ -9607,16 +9607,16 @@
         <v>15.5</v>
       </c>
       <c r="M119" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N119" t="n">
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>121.0040000000001</v>
+        <v>111.1630000000001</v>
       </c>
       <c r="P119" t="n">
-        <v>516.80101010101</v>
+        <v>516.8010101010101</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -9637,7 +9637,7 @@
         <v>0</v>
       </c>
       <c r="W119" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X119" t="n">
         <v>0</v>
@@ -9684,16 +9684,16 @@
         <v>17</v>
       </c>
       <c r="M120" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N120" t="n">
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>109.693</v>
+        <v>109.6929999999999</v>
       </c>
       <c r="P120" t="n">
-        <v>405.9999999999999</v>
+        <v>406.0000000000001</v>
       </c>
       <c r="Q120" t="n">
         <v>0</v>
@@ -9714,7 +9714,7 @@
         <v>0</v>
       </c>
       <c r="W120" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X120" t="n">
         <v>0</v>
@@ -9755,7 +9755,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>718.3716326530614</v>
+        <v>718.3716326530612</v>
       </c>
       <c r="L121" t="n">
         <v>118.3716326530612</v>
@@ -9764,10 +9764,10 @@
         <v>13.8592</v>
       </c>
       <c r="N121" t="n">
-        <v>600.0000000000001</v>
+        <v>600</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>5.627498467219993e-14</v>
       </c>
       <c r="P121" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
         <v>122.2324252627283</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P122" t="n">
         <v>121.010101010101</v>
@@ -9856,7 +9856,7 @@
         <v>0</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T122" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
         <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
+        <v>0.9999999999999982</v>
       </c>
       <c r="P123" t="n">
         <v>120</v>
@@ -9986,7 +9986,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>67.90418160162751</v>
+        <v>67.9041816016275</v>
       </c>
       <c r="L124" t="n">
         <v>84.38387755102042</v>
@@ -9995,10 +9995,10 @@
         <v>14.1452</v>
       </c>
       <c r="N124" t="n">
-        <v>1.020304050607095</v>
+        <v>1.020304050607081</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P124" t="n">
         <v>121.010101010101</v>
@@ -10042,7 +10042,7 @@
         <v>4</v>
       </c>
       <c r="D125" t="n">
-        <v>68.551</v>
+        <v>68.483</v>
       </c>
       <c r="E125" t="n">
         <v>38.078</v>
@@ -10063,10 +10063,10 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
-        <v>63.47163265306123</v>
+        <v>63.40224489795918</v>
       </c>
       <c r="L125" t="n">
-        <v>84.47163265306123</v>
+        <v>84.40224489795918</v>
       </c>
       <c r="M125" t="n">
         <v>15.2312</v>
@@ -10075,13 +10075,13 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>1</v>
+        <v>1.000000000000014</v>
       </c>
       <c r="P125" t="n">
         <v>120</v>
       </c>
       <c r="Q125" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
@@ -10140,22 +10140,22 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>563.7299176260648</v>
+        <v>584.2782032029219</v>
       </c>
       <c r="L126" t="n">
-        <v>85.42265306122449</v>
+        <v>85.42265306122444</v>
       </c>
       <c r="M126" t="n">
         <v>15.2312</v>
       </c>
       <c r="N126" t="n">
-        <v>504.8072645648403</v>
+        <v>525.3555501416974</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="P126" t="n">
-        <v>619.7591919191919</v>
+        <v>640.1019946402804</v>
       </c>
       <c r="Q126" t="n">
         <v>1</v>
@@ -10220,22 +10220,22 @@
         <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>28.99999999999999</v>
+        <v>29</v>
       </c>
       <c r="M127" t="n">
         <v>15.2312</v>
       </c>
       <c r="N127" t="n">
-        <v>1.06581410364015e-14</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>61.87720000000002</v>
+        <v>61.8772</v>
       </c>
       <c r="P127" t="n">
-        <v>557.2569696969697</v>
+        <v>577.5997724180581</v>
       </c>
       <c r="Q127" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
         <v>0</v>
@@ -10273,7 +10273,7 @@
         <v>7</v>
       </c>
       <c r="D128" t="n">
-        <v>75.066</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E128" t="n">
         <v>48.821</v>
@@ -10306,13 +10306,13 @@
         <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>67.6444</v>
+        <v>76.6964</v>
       </c>
       <c r="P128" t="n">
-        <v>488.929292929293</v>
+        <v>500.1286613069471</v>
       </c>
       <c r="Q128" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
         <v>0</v>
@@ -10374,22 +10374,22 @@
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>22.49999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="M129" t="n">
         <v>19.5284</v>
       </c>
       <c r="N129" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>81.5964</v>
+        <v>81.59639999999999</v>
       </c>
       <c r="P129" t="n">
-        <v>406.5086868686869</v>
+        <v>417.708055246341</v>
       </c>
       <c r="Q129" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
         <v>0</v>
@@ -10463,10 +10463,10 @@
         <v>142.0874</v>
       </c>
       <c r="P130" t="n">
-        <v>262.9860606060606</v>
+        <v>274.1854289837148</v>
       </c>
       <c r="Q130" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -10504,7 +10504,7 @@
         <v>10</v>
       </c>
       <c r="D131" t="n">
-        <v>125.853</v>
+        <v>138.408</v>
       </c>
       <c r="E131" t="n">
         <v>45.383</v>
@@ -10522,22 +10522,22 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>2.499999999999983</v>
+        <v>3.997576842982055</v>
       </c>
       <c r="M131" t="n">
         <v>18.1532</v>
       </c>
       <c r="N131" t="n">
-        <v>3.095167220167103e-14</v>
+        <v>-1.480297366166875e-14</v>
       </c>
       <c r="O131" t="n">
-        <v>141.5562</v>
+        <v>152.6435746938776</v>
       </c>
       <c r="P131" t="n">
         <v>120</v>
@@ -10599,7 +10599,7 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -10611,13 +10611,13 @@
         <v>18.1532</v>
       </c>
       <c r="N132" t="n">
-        <v>154.6134578104275</v>
+        <v>160.6131517192123</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P132" t="n">
-        <v>273.0673232323232</v>
+        <v>279.0070202020202</v>
       </c>
       <c r="Q132" t="n">
         <v>1</v>
@@ -10679,19 +10679,19 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
-        <v>6.500357142857088</v>
+        <v>0.5000510204081046</v>
       </c>
       <c r="L133" t="n">
-        <v>7.500357142857077</v>
+        <v>1.500051020408178</v>
       </c>
       <c r="M133" t="n">
         <v>19.8</v>
       </c>
       <c r="N133" t="n">
-        <v>5.741759480889699e-14</v>
+        <v>-2.870879740444849e-14</v>
       </c>
       <c r="O133" t="n">
-        <v>151.5366500000001</v>
+        <v>157.41695</v>
       </c>
       <c r="P133" t="n">
         <v>120</v>
@@ -10735,7 +10735,7 @@
         <v>13</v>
       </c>
       <c r="D134" t="n">
-        <v>139.087</v>
+        <v>136.236</v>
       </c>
       <c r="E134" t="n">
         <v>56.911</v>
@@ -10753,25 +10753,25 @@
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K134" t="n">
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>165.1544897959184</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M134" t="n">
         <v>22.7644</v>
       </c>
       <c r="N134" t="n">
-        <v>1.000000000000739</v>
+        <v>2.020202020202021</v>
       </c>
       <c r="O134" t="n">
-        <v>1.176059249985428e-14</v>
+        <v>4.39648317751562e-16</v>
       </c>
       <c r="P134" t="n">
-        <v>120.9900000000007</v>
+        <v>122</v>
       </c>
       <c r="Q134" t="n">
         <v>1</v>
@@ -10830,28 +10830,28 @@
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>162.2453061224488</v>
+        <v>160.2248979591837</v>
       </c>
       <c r="M135" t="n">
         <v>22.7644</v>
       </c>
       <c r="N135" t="n">
-        <v>1.500000000000171</v>
+        <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>6.924461004587101e-14</v>
+        <v>1.98</v>
       </c>
       <c r="P135" t="n">
-        <v>122.4750000000008</v>
+        <v>120</v>
       </c>
       <c r="Q135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
         <v>0</v>
@@ -10907,25 +10907,25 @@
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K136" t="n">
         <v>0</v>
       </c>
       <c r="L136" t="n">
-        <v>147.1748979591835</v>
+        <v>147.1748979591837</v>
       </c>
       <c r="M136" t="n">
         <v>21.4324</v>
       </c>
       <c r="N136" t="n">
-        <v>114.2766059791859</v>
+        <v>170.9880666071145</v>
       </c>
       <c r="O136" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>235.6088399193947</v>
+        <v>289.2781859410433</v>
       </c>
       <c r="Q136" t="n">
         <v>1</v>
@@ -10966,7 +10966,7 @@
         <v>16</v>
       </c>
       <c r="D137" t="n">
-        <v>122.799</v>
+        <v>140.444</v>
       </c>
       <c r="E137" t="n">
         <v>41.57</v>
@@ -10984,37 +10984,37 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>142.2724489795918</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M137" t="n">
         <v>16.628</v>
       </c>
       <c r="N137" t="n">
-        <v>583.5051020408165</v>
+        <v>596.9999999999997</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>5.627498467219993e-14</v>
       </c>
       <c r="P137" t="n">
-        <v>813.278890939803</v>
+        <v>880.3081859410429</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.9999999999999993</v>
+        <v>1</v>
       </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
       <c r="S137" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T137" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U137" t="n">
         <v>0</v>
@@ -11061,28 +11061,28 @@
         <v>0</v>
       </c>
       <c r="J138" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K138" t="n">
         <v>0</v>
       </c>
       <c r="L138" t="n">
-        <v>107.2571428571515</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M138" t="n">
         <v>16.628</v>
       </c>
       <c r="N138" t="n">
-        <v>-8.355982572538778e-12</v>
+        <v>9.479591836734727</v>
       </c>
       <c r="O138" t="n">
-        <v>51.95999999999148</v>
+        <v>4.748201831716869e-14</v>
       </c>
       <c r="P138" t="n">
-        <v>760.7940424549548</v>
+        <v>889.6929818594102</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" t="n">
         <v>0</v>
@@ -11138,28 +11138,28 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>103.2343856832605</v>
+        <v>118.214081632653</v>
       </c>
       <c r="M139" t="n">
         <v>19.5068</v>
       </c>
       <c r="N139" t="n">
-        <v>-3.126388037344441e-13</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="O139" t="n">
-        <v>41.14010203040488</v>
+        <v>26.46000000000012</v>
       </c>
       <c r="P139" t="n">
-        <v>719.2383838383839</v>
+        <v>862.9657091321374</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R139" t="n">
         <v>0</v>
@@ -11197,7 +11197,7 @@
         <v>19</v>
       </c>
       <c r="D140" t="n">
-        <v>122.803</v>
+        <v>117.645</v>
       </c>
       <c r="E140" t="n">
         <v>43.091</v>
@@ -11227,13 +11227,13 @@
         <v>17.2364</v>
       </c>
       <c r="N140" t="n">
-        <v>-9.689219124001366e-14</v>
+        <v>8.612639221334548e-14</v>
       </c>
       <c r="O140" t="n">
-        <v>110.6394</v>
+        <v>105.4814</v>
       </c>
       <c r="P140" t="n">
-        <v>607.4814141414141</v>
+        <v>756.4188404452688</v>
       </c>
       <c r="Q140" t="n">
         <v>-0</v>
@@ -11242,10 +11242,10 @@
         <v>0</v>
       </c>
       <c r="S140" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T140" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U140" t="n">
         <v>0</v>
@@ -11298,19 +11298,19 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>38.99999999999999</v>
+        <v>38.99999999999996</v>
       </c>
       <c r="M141" t="n">
         <v>17.2364</v>
       </c>
       <c r="N141" t="n">
-        <v>5.024039545778486e-14</v>
+        <v>-2.153159805333638e-14</v>
       </c>
       <c r="O141" t="n">
-        <v>96.66139999999999</v>
+        <v>96.66140000000003</v>
       </c>
       <c r="P141" t="n">
-        <v>509.8436363636364</v>
+        <v>658.7810626674909</v>
       </c>
       <c r="Q141" t="n">
         <v>-0</v>
@@ -11319,10 +11319,10 @@
         <v>0</v>
       </c>
       <c r="S141" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T141" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U141" t="n">
         <v>0</v>
@@ -11375,19 +11375,19 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>41</v>
+        <v>40.99999999999998</v>
       </c>
       <c r="M142" t="n">
         <v>17.85</v>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>2.131628207280301e-14</v>
       </c>
       <c r="O142" t="n">
-        <v>97.554</v>
+        <v>97.55400000000003</v>
       </c>
       <c r="P142" t="n">
-        <v>411.3042424242424</v>
+        <v>560.241668728097</v>
       </c>
       <c r="Q142" t="n">
         <v>-0</v>
@@ -11428,7 +11428,7 @@
         <v>22</v>
       </c>
       <c r="D143" t="n">
-        <v>119.884</v>
+        <v>110.043</v>
       </c>
       <c r="E143" t="n">
         <v>40.775</v>
@@ -11452,19 +11452,19 @@
         <v>0</v>
       </c>
       <c r="L143" t="n">
-        <v>37</v>
+        <v>37.00000000000004</v>
       </c>
       <c r="M143" t="n">
         <v>16.31</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-14</v>
       </c>
       <c r="O143" t="n">
-        <v>99.934</v>
+        <v>90.09299999999998</v>
       </c>
       <c r="P143" t="n">
-        <v>310.3608080808081</v>
+        <v>469.2386384250667</v>
       </c>
       <c r="Q143" t="n">
         <v>-0</v>
@@ -11473,10 +11473,10 @@
         <v>0</v>
       </c>
       <c r="S143" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T143" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U143" t="n">
         <v>0</v>
@@ -11541,7 +11541,7 @@
         <v>96.46300000000001</v>
       </c>
       <c r="P144" t="n">
-        <v>212.9234343434343</v>
+        <v>371.801264687693</v>
       </c>
       <c r="Q144" t="n">
         <v>-0</v>
@@ -11550,10 +11550,10 @@
         <v>0</v>
       </c>
       <c r="S144" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T144" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U144" t="n">
         <v>0</v>
@@ -11618,7 +11618,7 @@
         <v>91.99420000000001</v>
       </c>
       <c r="P145" t="n">
-        <v>120</v>
+        <v>278.8778303442587</v>
       </c>
       <c r="Q145" t="n">
         <v>-0</v>
@@ -11627,10 +11627,10 @@
         <v>0</v>
       </c>
       <c r="S145" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T145" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U145" t="n">
         <v>0</v>
@@ -11680,7 +11680,7 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>305.851227821401</v>
+        <v>305.8512278214009</v>
       </c>
       <c r="L146" t="n">
         <v>84.38387755102042</v>
@@ -11689,13 +11689,13 @@
         <v>14.1452</v>
       </c>
       <c r="N146" t="n">
-        <v>243.9673502703806</v>
+        <v>243.9673502703805</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P146" t="n">
-        <v>241.5276767676768</v>
+        <v>241.5276767676767</v>
       </c>
       <c r="Q146" t="n">
         <v>1</v>
@@ -11704,7 +11704,7 @@
         <v>0</v>
       </c>
       <c r="S146" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T146" t="n">
         <v>0</v>
@@ -11772,7 +11772,7 @@
         <v>59.6662</v>
       </c>
       <c r="P147" t="n">
-        <v>181.2587878787879</v>
+        <v>181.2587878787878</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
@@ -11846,7 +11846,7 @@
         <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>60.64620000000001</v>
+        <v>60.64619999999996</v>
       </c>
       <c r="P148" t="n">
         <v>120</v>
@@ -12142,7 +12142,7 @@
         <v>0</v>
       </c>
       <c r="K152" t="n">
-        <v>266.9917112164731</v>
+        <v>266.991711216473</v>
       </c>
       <c r="L152" t="n">
         <v>105.7616326530612</v>
@@ -12151,13 +12151,13 @@
         <v>19.5284</v>
       </c>
       <c r="N152" t="n">
-        <v>183.2300785634119</v>
+        <v>183.2300785634118</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
       </c>
       <c r="P152" t="n">
-        <v>301.3977777777778</v>
+        <v>301.3977777777777</v>
       </c>
       <c r="Q152" t="n">
         <v>1</v>
@@ -12231,7 +12231,7 @@
         <v>0</v>
       </c>
       <c r="O153" t="n">
-        <v>73.75640000000001</v>
+        <v>73.75639999999996</v>
       </c>
       <c r="P153" t="n">
         <v>226.8963636363636</v>
@@ -12299,16 +12299,16 @@
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>45.49999999999999</v>
+        <v>45.49999999999994</v>
       </c>
       <c r="M154" t="n">
         <v>24.5644</v>
       </c>
       <c r="N154" t="n">
-        <v>3.588599675556061e-14</v>
+        <v>7.894919286223335e-14</v>
       </c>
       <c r="O154" t="n">
-        <v>105.8274</v>
+        <v>105.8274000000001</v>
       </c>
       <c r="P154" t="n">
         <v>120</v>
@@ -12370,10 +12370,10 @@
         <v>0</v>
       </c>
       <c r="J155" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K155" t="n">
-        <v>104.7563265306122</v>
+        <v>103.2587496876302</v>
       </c>
       <c r="L155" t="n">
         <v>159.7563265306122</v>
@@ -12382,10 +12382,10 @@
         <v>18.1532</v>
       </c>
       <c r="N155" t="n">
-        <v>0.9999999999999661</v>
+        <v>0.9999999999999877</v>
       </c>
       <c r="O155" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P155" t="n">
         <v>120.99</v>
@@ -12447,7 +12447,7 @@
         <v>63.5</v>
       </c>
       <c r="J156" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -12456,16 +12456,16 @@
         <v>159.7563265306122</v>
       </c>
       <c r="M156" t="n">
-        <v>18.1532</v>
+        <v>18.15319999999999</v>
       </c>
       <c r="N156" t="n">
-        <v>154.1134578104275</v>
+        <v>160.1131517192124</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="P156" t="n">
-        <v>273.5623232323232</v>
+        <v>279.5020202020202</v>
       </c>
       <c r="Q156" t="n">
         <v>1</v>
@@ -12486,7 +12486,7 @@
         <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>45.383</v>
+        <v>45.38299999999998</v>
       </c>
       <c r="X156" t="n">
         <v>0</v>
@@ -12536,13 +12536,13 @@
         <v>19.8</v>
       </c>
       <c r="N157" t="n">
-        <v>2.870879740444849e-14</v>
+        <v>-2.512019772889243e-14</v>
       </c>
       <c r="O157" t="n">
-        <v>93.227</v>
+        <v>93.22699999999999</v>
       </c>
       <c r="P157" t="n">
-        <v>179.3936363636363</v>
+        <v>185.3333333333333</v>
       </c>
       <c r="Q157" t="n">
         <v>0</v>
@@ -12595,13 +12595,13 @@
         <v>68</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>0.47979797979797</v>
       </c>
       <c r="I158" t="n">
-        <v>68</v>
+        <v>67.52020202020203</v>
       </c>
       <c r="J158" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -12613,16 +12613,16 @@
         <v>22.7644</v>
       </c>
       <c r="N158" t="n">
-        <v>2.409183673470128</v>
+        <v>1.000000000000016</v>
       </c>
       <c r="O158" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P158" t="n">
-        <v>181.7787282003718</v>
+        <v>186.3233333333334</v>
       </c>
       <c r="Q158" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R158" t="n">
         <v>0</v>
@@ -12672,13 +12672,13 @@
         <v>70</v>
       </c>
       <c r="H159" t="n">
-        <v>70</v>
+        <v>5.52040816326531</v>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>64.47959183673468</v>
       </c>
       <c r="J159" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K159" t="n">
         <v>0</v>
@@ -12690,16 +12690,16 @@
         <v>22.7644</v>
       </c>
       <c r="N159" t="n">
-        <v>68.99999999999997</v>
+        <v>1.000000000000027</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P159" t="n">
-        <v>250.0887282003717</v>
+        <v>187.3133333333334</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R159" t="n">
         <v>0</v>
@@ -12749,13 +12749,13 @@
         <v>70.5</v>
       </c>
       <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
         <v>70.5</v>
       </c>
-      <c r="I160" t="n">
-        <v>0</v>
-      </c>
       <c r="J160" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -12767,13 +12767,13 @@
         <v>21.4324</v>
       </c>
       <c r="N160" t="n">
-        <v>178.2766059791857</v>
+        <v>164.4880666071145</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
       </c>
       <c r="P160" t="n">
-        <v>426.5825681197655</v>
+        <v>350.1565192743766</v>
       </c>
       <c r="Q160" t="n">
         <v>1</v>
@@ -12826,31 +12826,31 @@
         <v>67.5</v>
       </c>
       <c r="H161" t="n">
-        <v>24.20952715175196</v>
+        <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>43.29047284824804</v>
+        <v>67.5</v>
       </c>
       <c r="J161" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
       </c>
       <c r="L161" t="n">
-        <v>160.2775510204082</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M161" t="n">
         <v>16.628</v>
       </c>
       <c r="N161" t="n">
-        <v>579.209527151752</v>
+        <v>586.4999999999997</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P161" t="n">
-        <v>1000</v>
+        <v>930.7915192743762</v>
       </c>
       <c r="Q161" t="n">
         <v>1</v>
@@ -12871,7 +12871,7 @@
         <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X161" t="n">
         <v>0</v>
@@ -12909,28 +12909,28 @@
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>159.257142857143</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M162" t="n">
         <v>16.628</v>
       </c>
       <c r="N162" t="n">
-        <v>-1.159566270164052e-13</v>
+        <v>61.47959183673471</v>
       </c>
       <c r="O162" t="n">
-        <v>0.9999999999999147</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P162" t="n">
-        <v>998.989898989899</v>
+        <v>991.6563151927436</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R162" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
         <v>0</v>
       </c>
       <c r="W162" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X162" t="n">
         <v>0</v>
@@ -12980,13 +12980,13 @@
         <v>57.5</v>
       </c>
       <c r="H163" t="n">
-        <v>57.5</v>
+        <v>49.92796445177413</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>7.57203554822587</v>
       </c>
       <c r="J163" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -12998,7 +12998,7 @@
         <v>19.5068</v>
       </c>
       <c r="N163" t="n">
-        <v>1.02030405060711</v>
+        <v>8.42796445177415</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -13069,19 +13069,19 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>56.00000000000004</v>
+        <v>56.00000000000002</v>
       </c>
       <c r="M164" t="n">
         <v>17.2364</v>
       </c>
       <c r="N164" t="n">
-        <v>-2.870879740444848e-14</v>
+        <v>-1.14835189617794e-13</v>
       </c>
       <c r="O164" t="n">
-        <v>80.00139999999996</v>
+        <v>80.00139999999998</v>
       </c>
       <c r="P164" t="n">
-        <v>919.1905050505051</v>
+        <v>919.190505050505</v>
       </c>
       <c r="Q164" t="n">
         <v>-0</v>
@@ -13108,7 +13108,7 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -13146,16 +13146,16 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>55.49999999999998</v>
+        <v>55.50000000000002</v>
       </c>
       <c r="M165" t="n">
         <v>17.2364</v>
       </c>
       <c r="N165" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>5.7417594808897e-14</v>
       </c>
       <c r="O165" t="n">
-        <v>80.4914</v>
+        <v>80.49139999999997</v>
       </c>
       <c r="P165" t="n">
         <v>837.8860606060606</v>
@@ -13185,7 +13185,7 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -13244,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="S166" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T166" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U166" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>61.5</v>
       </c>
       <c r="M167" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N167" t="n">
         <v>0</v>
@@ -13324,16 +13324,16 @@
         <v>0</v>
       </c>
       <c r="T167" t="n">
-        <v>-0</v>
+        <v>2.368475785867e-14</v>
       </c>
       <c r="U167" t="n">
-        <v>0</v>
+        <v>2.131628207280301e-14</v>
       </c>
       <c r="V167" t="n">
         <v>0</v>
       </c>
       <c r="W167" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X167" t="n">
         <v>0</v>
@@ -13398,7 +13398,7 @@
         <v>0</v>
       </c>
       <c r="S168" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T168" t="n">
         <v>0</v>
@@ -13475,10 +13475,10 @@
         <v>0</v>
       </c>
       <c r="S169" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U169" t="n">
         <v>0</v>
@@ -13493,7 +13493,7 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0.9999999999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -13519,10 +13519,10 @@
         <v>206.5</v>
       </c>
       <c r="H170" t="n">
-        <v>205.5959987631417</v>
+        <v>205.5959987631416</v>
       </c>
       <c r="I170" t="n">
-        <v>0.9040012368583348</v>
+        <v>0.9040012368583632</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -13537,10 +13537,10 @@
         <v>14.1452</v>
       </c>
       <c r="N170" t="n">
-        <v>121.2121212121213</v>
+        <v>121.2121212121212</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P170" t="n">
         <v>120</v>
@@ -13596,10 +13596,10 @@
         <v>228.5</v>
       </c>
       <c r="H171" t="n">
-        <v>86.42448565223464</v>
+        <v>85.40418160162756</v>
       </c>
       <c r="I171" t="n">
-        <v>142.0755143477654</v>
+        <v>143.0958183983724</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -13614,13 +13614,13 @@
         <v>14.1452</v>
       </c>
       <c r="N171" t="n">
-        <v>2.040608101214218</v>
+        <v>1.020304050607137</v>
       </c>
       <c r="O171" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P171" t="n">
-        <v>122.0202020202021</v>
+        <v>121.0101010101011</v>
       </c>
       <c r="Q171" t="n">
         <v>1</v>
@@ -13673,7 +13673,7 @@
         <v>229.5</v>
       </c>
       <c r="H172" t="n">
-        <v>83.3634693877551</v>
+        <v>83.36346938775509</v>
       </c>
       <c r="I172" t="n">
         <v>146.1365306122449</v>
@@ -13691,13 +13691,13 @@
         <v>14.1452</v>
       </c>
       <c r="N172" t="n">
-        <v>-2.242874797222539e-16</v>
+        <v>-1.637298601972453e-14</v>
       </c>
       <c r="O172" t="n">
-        <v>1</v>
+        <v>0.9999999999999982</v>
       </c>
       <c r="P172" t="n">
-        <v>121.0101010101011</v>
+        <v>120</v>
       </c>
       <c r="Q172" t="n">
         <v>-0</v>
@@ -13750,10 +13750,10 @@
         <v>200.5</v>
       </c>
       <c r="H173" t="n">
-        <v>84.40224489795915</v>
+        <v>87.50386926365272</v>
       </c>
       <c r="I173" t="n">
-        <v>116.0977551020408</v>
+        <v>112.9961307363473</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -13762,22 +13762,22 @@
         <v>0</v>
       </c>
       <c r="L173" t="n">
-        <v>84.40224489795919</v>
+        <v>85.42265306122449</v>
       </c>
       <c r="M173" t="n">
-        <v>15.2312</v>
+        <v>15.23119999999999</v>
       </c>
       <c r="N173" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>2.081216202428223</v>
       </c>
       <c r="O173" t="n">
-        <v>1</v>
+        <v>-1.06581410364015e-14</v>
       </c>
       <c r="P173" t="n">
-        <v>120.0000000000001</v>
+        <v>122.060404040404</v>
       </c>
       <c r="Q173" t="n">
-        <v>-0</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="R173" t="n">
         <v>0</v>
@@ -13795,7 +13795,7 @@
         <v>0</v>
       </c>
       <c r="W173" t="n">
-        <v>38.078</v>
+        <v>38.07799999999997</v>
       </c>
       <c r="X173" t="n">
         <v>0</v>
@@ -13827,7 +13827,7 @@
         <v>187</v>
       </c>
       <c r="H174" t="n">
-        <v>86.42265306122449</v>
+        <v>86.42265306122448</v>
       </c>
       <c r="I174" t="n">
         <v>100.5773469387755</v>
@@ -13839,19 +13839,19 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>85.42265306122449</v>
+        <v>85.42265306122448</v>
       </c>
       <c r="M174" t="n">
-        <v>15.2312</v>
+        <v>15.23119999999999</v>
       </c>
       <c r="N174" t="n">
         <v>1</v>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P174" t="n">
-        <v>120.9900000000001</v>
+        <v>123.050404040404</v>
       </c>
       <c r="Q174" t="n">
         <v>1</v>
@@ -13872,7 +13872,7 @@
         <v>0</v>
       </c>
       <c r="W174" t="n">
-        <v>38.078</v>
+        <v>38.07799999999997</v>
       </c>
       <c r="X174" t="n">
         <v>0</v>
@@ -13904,10 +13904,10 @@
         <v>173.5</v>
       </c>
       <c r="H175" t="n">
-        <v>93.14000000000001</v>
+        <v>91.11959183673468</v>
       </c>
       <c r="I175" t="n">
-        <v>80.35999999999999</v>
+        <v>82.38040816326532</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -13916,22 +13916,22 @@
         <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>92.14</v>
+        <v>91.11959183673468</v>
       </c>
       <c r="M175" t="n">
-        <v>15.2312</v>
+        <v>15.23119999999999</v>
       </c>
       <c r="N175" t="n">
-        <v>1.000000000000014</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
-        <v>0</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="P175" t="n">
-        <v>121.9800000000001</v>
+        <v>122.040303030303</v>
       </c>
       <c r="Q175" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="R175" t="n">
         <v>0</v>
@@ -13949,7 +13949,7 @@
         <v>0</v>
       </c>
       <c r="W175" t="n">
-        <v>38.078</v>
+        <v>38.07799999999997</v>
       </c>
       <c r="X175" t="n">
         <v>0</v>
@@ -13981,10 +13981,10 @@
         <v>155.5</v>
       </c>
       <c r="H176" t="n">
-        <v>106.7616326530612</v>
+        <v>104.7412244897959</v>
       </c>
       <c r="I176" t="n">
-        <v>48.73836734693877</v>
+        <v>50.75877551020407</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -13993,22 +13993,22 @@
         <v>0</v>
       </c>
       <c r="L176" t="n">
-        <v>105.7616326530612</v>
+        <v>104.7412244897959</v>
       </c>
       <c r="M176" t="n">
         <v>19.5284</v>
       </c>
       <c r="N176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>0</v>
+        <v>0.9999999999999964</v>
       </c>
       <c r="P176" t="n">
-        <v>122.9700000000001</v>
+        <v>121.030202020202</v>
       </c>
       <c r="Q176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
@@ -14079,10 +14079,10 @@
         <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>-3.552713678800501e-15</v>
       </c>
       <c r="P177" t="n">
-        <v>123.9600000000001</v>
+        <v>122.020202020202</v>
       </c>
       <c r="Q177" t="n">
         <v>1</v>
@@ -14135,10 +14135,10 @@
         <v>229</v>
       </c>
       <c r="H178" t="n">
-        <v>152.4667346938776</v>
+        <v>152.4667346938775</v>
       </c>
       <c r="I178" t="n">
-        <v>76.53326530612244</v>
+        <v>76.53326530612247</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14153,16 +14153,16 @@
         <v>24.5644</v>
       </c>
       <c r="N178" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>1</v>
+        <v>1.000000000000011</v>
       </c>
       <c r="P178" t="n">
-        <v>122.9498989898991</v>
+        <v>121.010101010101</v>
       </c>
       <c r="Q178" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R178" t="n">
         <v>0</v>
@@ -14212,13 +14212,13 @@
         <v>246.5</v>
       </c>
       <c r="H179" t="n">
-        <v>158.7359183673469</v>
+        <v>157.2383415243648</v>
       </c>
       <c r="I179" t="n">
-        <v>87.76408163265307</v>
+        <v>89.26165847563516</v>
       </c>
       <c r="J179" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K179" t="n">
         <v>0</v>
@@ -14227,16 +14227,16 @@
         <v>158.7359183673469</v>
       </c>
       <c r="M179" t="n">
-        <v>18.1532</v>
+        <v>18.15319999999999</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>-1.332267629550188e-14</v>
       </c>
       <c r="O179" t="n">
-        <v>0.9999999999949918</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="P179" t="n">
-        <v>121.9397979798031</v>
+        <v>120</v>
       </c>
       <c r="Q179" t="n">
         <v>-0</v>
@@ -14257,7 +14257,7 @@
         <v>0</v>
       </c>
       <c r="W179" t="n">
-        <v>45.383</v>
+        <v>45.38299999999998</v>
       </c>
       <c r="X179" t="n">
         <v>0</v>
@@ -14295,25 +14295,25 @@
         <v>266.5</v>
       </c>
       <c r="J180" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
       </c>
       <c r="L180" t="n">
-        <v>159.7563265306173</v>
+        <v>159.7563265306122</v>
       </c>
       <c r="M180" t="n">
         <v>18.1532</v>
       </c>
       <c r="N180" t="n">
-        <v>154.1134578104225</v>
+        <v>160.1131517192124</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
       </c>
       <c r="P180" t="n">
-        <v>274.5121212121214</v>
+        <v>278.5120202020203</v>
       </c>
       <c r="Q180" t="n">
         <v>1</v>
@@ -14325,7 +14325,7 @@
         <v>0</v>
       </c>
       <c r="T180" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U180" t="n">
         <v>0</v>
@@ -14366,10 +14366,10 @@
         <v>293.5</v>
       </c>
       <c r="H181" t="n">
-        <v>163.1295918367347</v>
+        <v>139.9353019575181</v>
       </c>
       <c r="I181" t="n">
-        <v>130.3704081632653</v>
+        <v>153.5646980424819</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -14378,22 +14378,22 @@
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>162.1295918367347</v>
+        <v>139.9353019575181</v>
       </c>
       <c r="M181" t="n">
         <v>19.8</v>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O181" t="n">
-        <v>-9.01279051390702e-15</v>
+        <v>21.75040408163235</v>
       </c>
       <c r="P181" t="n">
-        <v>275.5021212121214</v>
+        <v>256.5419150690583</v>
       </c>
       <c r="Q181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R181" t="n">
         <v>0</v>
@@ -14402,7 +14402,7 @@
         <v>0</v>
       </c>
       <c r="T181" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U181" t="n">
         <v>0</v>
@@ -14443,31 +14443,31 @@
         <v>306</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>0.4797979797979688</v>
       </c>
       <c r="I182" t="n">
-        <v>306</v>
+        <v>305.520202020202</v>
       </c>
       <c r="J182" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K182" t="n">
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>162.2453061224489</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M182" t="n">
         <v>22.7644</v>
       </c>
       <c r="N182" t="n">
-        <v>2.409183673470153</v>
+        <v>0.9999999999999896</v>
       </c>
       <c r="O182" t="n">
-        <v>5.275779813018744e-14</v>
+        <v>3.70403707705691e-14</v>
       </c>
       <c r="P182" t="n">
-        <v>277.8872130488568</v>
+        <v>257.5319150690582</v>
       </c>
       <c r="Q182" t="n">
         <v>1</v>
@@ -14520,34 +14520,34 @@
         <v>293.5</v>
       </c>
       <c r="H183" t="n">
-        <v>1.999999999999737</v>
+        <v>3.499999999999943</v>
       </c>
       <c r="I183" t="n">
-        <v>291.5000000000003</v>
+        <v>290.0000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K183" t="n">
         <v>0</v>
       </c>
       <c r="L183" t="n">
-        <v>162.245306122449</v>
+        <v>161.2248979591837</v>
       </c>
       <c r="M183" t="n">
         <v>22.7644</v>
       </c>
       <c r="N183" t="n">
-        <v>1.000000000000009</v>
+        <v>-2.175588553305862e-14</v>
       </c>
       <c r="O183" t="n">
-        <v>0</v>
+        <v>1.000000000000007</v>
       </c>
       <c r="P183" t="n">
-        <v>278.8772130488568</v>
+        <v>256.5218140589572</v>
       </c>
       <c r="Q183" t="n">
-        <v>0.9999999999999998</v>
+        <v>-0</v>
       </c>
       <c r="R183" t="n">
         <v>0</v>
@@ -14603,7 +14603,7 @@
         <v>295</v>
       </c>
       <c r="J184" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -14615,13 +14615,13 @@
         <v>21.4324</v>
       </c>
       <c r="N184" t="n">
-        <v>107.7766059791857</v>
+        <v>164.4880666071144</v>
       </c>
       <c r="O184" t="n">
         <v>0</v>
       </c>
       <c r="P184" t="n">
-        <v>385.5760529682506</v>
+        <v>419.3650000000005</v>
       </c>
       <c r="Q184" t="n">
         <v>1</v>
@@ -14680,28 +14680,28 @@
         <v>280</v>
       </c>
       <c r="J185" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K185" t="n">
         <v>0</v>
       </c>
       <c r="L185" t="n">
-        <v>160.2775510204082</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M185" t="n">
         <v>16.628</v>
       </c>
       <c r="N185" t="n">
-        <v>555.0000000000001</v>
+        <v>586.4999999999997</v>
       </c>
       <c r="O185" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P185" t="n">
-        <v>935.0260529682507</v>
+        <v>1000</v>
       </c>
       <c r="Q185" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="R185" t="n">
         <v>0</v>
@@ -14710,7 +14710,7 @@
         <v>0</v>
       </c>
       <c r="T185" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U185" t="n">
         <v>0</v>
@@ -14719,7 +14719,7 @@
         <v>0</v>
       </c>
       <c r="W185" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X185" t="n">
         <v>0</v>
@@ -14751,34 +14751,34 @@
         <v>222</v>
       </c>
       <c r="H186" t="n">
-        <v>64.52040816326507</v>
+        <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>157.4795918367349</v>
+        <v>222</v>
       </c>
       <c r="J186" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K186" t="n">
         <v>0</v>
       </c>
       <c r="L186" t="n">
-        <v>160.2775510204082</v>
+        <v>159.2571428571428</v>
       </c>
       <c r="M186" t="n">
         <v>16.628</v>
       </c>
       <c r="N186" t="n">
-        <v>1.000000000000009</v>
+        <v>-7.177199351112124e-15</v>
       </c>
       <c r="O186" t="n">
-        <v>0</v>
+        <v>1.000000000000011</v>
       </c>
       <c r="P186" t="n">
-        <v>936.0160529682507</v>
+        <v>998.9898989898991</v>
       </c>
       <c r="Q186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
         <v>0</v>
@@ -14787,7 +14787,7 @@
         <v>0</v>
       </c>
       <c r="T186" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U186" t="n">
         <v>0</v>
@@ -14796,7 +14796,7 @@
         <v>0</v>
       </c>
       <c r="W186" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X186" t="n">
         <v>0</v>
@@ -14828,13 +14828,13 @@
         <v>155.5</v>
       </c>
       <c r="H187" t="n">
-        <v>55.45928778612756</v>
+        <v>40.47959183673481</v>
       </c>
       <c r="I187" t="n">
-        <v>100.0407122138724</v>
+        <v>115.0204081632652</v>
       </c>
       <c r="J187" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -14852,10 +14852,10 @@
         <v>1</v>
       </c>
       <c r="P187" t="n">
-        <v>935.0059519581497</v>
+        <v>997.979797979798</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R187" t="n">
         <v>0</v>
@@ -14923,16 +14923,16 @@
         <v>17.2364</v>
       </c>
       <c r="N188" t="n">
-        <v>-5.741759480889698e-14</v>
+        <v>-1.435439870222425e-14</v>
       </c>
       <c r="O188" t="n">
-        <v>4.541399999999982</v>
+        <v>4.541400000000021</v>
       </c>
       <c r="P188" t="n">
-        <v>930.4186792308769</v>
+        <v>993.3925252525253</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R188" t="n">
         <v>0</v>
@@ -14982,10 +14982,10 @@
         <v>139</v>
       </c>
       <c r="H189" t="n">
-        <v>139</v>
+        <v>136.613673469388</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>2.386326530611996</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -14994,22 +14994,22 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>137.6340816326531</v>
+        <v>136.6136734693877</v>
       </c>
       <c r="M189" t="n">
         <v>17.2364</v>
       </c>
       <c r="N189" t="n">
-        <v>1.365918367346836</v>
+        <v>1.004807909155697e-13</v>
       </c>
       <c r="O189" t="n">
-        <v>0</v>
+        <v>1.000000000000011</v>
       </c>
       <c r="P189" t="n">
-        <v>931.7709384145503</v>
+        <v>992.3824242424243</v>
       </c>
       <c r="Q189" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="R189" t="n">
         <v>0</v>
@@ -15059,10 +15059,10 @@
         <v>150</v>
       </c>
       <c r="H190" t="n">
-        <v>141.5448979591837</v>
+        <v>139.5244897959184</v>
       </c>
       <c r="I190" t="n">
-        <v>8.455102040816286</v>
+        <v>10.47551020408162</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15071,22 +15071,22 @@
         <v>0</v>
       </c>
       <c r="L190" t="n">
-        <v>140.5448979591837</v>
+        <v>139.5244897959184</v>
       </c>
       <c r="M190" t="n">
         <v>17.85</v>
       </c>
       <c r="N190" t="n">
-        <v>1.000000000000028</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>0</v>
+        <v>0.9999999999999929</v>
       </c>
       <c r="P190" t="n">
-        <v>932.7609384145503</v>
+        <v>991.3723232323233</v>
       </c>
       <c r="Q190" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="R190" t="n">
         <v>0</v>
@@ -15136,10 +15136,10 @@
         <v>155</v>
       </c>
       <c r="H191" t="n">
-        <v>129.9316326530612</v>
+        <v>127.9112244897959</v>
       </c>
       <c r="I191" t="n">
-        <v>25.06836734693877</v>
+        <v>27.08877551020409</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15148,22 +15148,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>128.9316326530612</v>
+        <v>127.9112244897959</v>
       </c>
       <c r="M191" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>0</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="P191" t="n">
-        <v>933.7509384145503</v>
+        <v>990.3622222222223</v>
       </c>
       <c r="Q191" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="R191" t="n">
         <v>0</v>
@@ -15181,7 +15181,7 @@
         <v>0</v>
       </c>
       <c r="W191" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X191" t="n">
         <v>0</v>
@@ -15213,10 +15213,10 @@
         <v>176</v>
       </c>
       <c r="H192" t="n">
-        <v>156.2215093318293</v>
+        <v>127.9112244897959</v>
       </c>
       <c r="I192" t="n">
-        <v>19.77849066817075</v>
+        <v>48.08877551020409</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15225,22 +15225,22 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>128.9316326530612</v>
+        <v>127.9112244897959</v>
       </c>
       <c r="M192" t="n">
-        <v>16.31</v>
+        <v>16.30999999999999</v>
       </c>
       <c r="N192" t="n">
-        <v>27.28987667876802</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>0</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="P192" t="n">
-        <v>960.7679163265307</v>
+        <v>989.3521212121212</v>
       </c>
       <c r="Q192" t="n">
-        <v>1</v>
+        <v>-0</v>
       </c>
       <c r="R192" t="n">
         <v>0</v>
@@ -15258,7 +15258,7 @@
         <v>0</v>
       </c>
       <c r="W192" t="n">
-        <v>40.775</v>
+        <v>40.77499999999998</v>
       </c>
       <c r="X192" t="n">
         <v>0</v>
@@ -15290,10 +15290,10 @@
         <v>158</v>
       </c>
       <c r="H193" t="n">
-        <v>158</v>
+        <v>129.1270657721308</v>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>28.87293422786919</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15308,7 +15308,7 @@
         <v>13.8592</v>
       </c>
       <c r="N193" t="n">
-        <v>39.62836734693877</v>
+        <v>10.75543311906958</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -15388,7 +15388,7 @@
         <v>121.2121212121212</v>
       </c>
       <c r="O194" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P194" t="n">
         <v>120</v>
@@ -15400,7 +15400,7 @@
         <v>0</v>
       </c>
       <c r="S194" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T194" t="n">
         <v>0</v>
@@ -15462,7 +15462,7 @@
         <v>14.1452</v>
       </c>
       <c r="N195" t="n">
-        <v>68.39730639730641</v>
+        <v>68.39730639730638</v>
       </c>
       <c r="O195" t="n">
         <v>0</v>
@@ -15542,13 +15542,13 @@
         <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>66.03620000000001</v>
+        <v>66.03619999999998</v>
       </c>
       <c r="P196" t="n">
         <v>121.010101010101</v>
       </c>
       <c r="Q196" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
         <v>0</v>
@@ -15779,7 +15779,7 @@
         <v>273.4573737373738</v>
       </c>
       <c r="Q199" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R199" t="n">
         <v>0</v>
@@ -15856,7 +15856,7 @@
         <v>195.4913131313131</v>
       </c>
       <c r="Q200" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R200" t="n">
         <v>0</v>
@@ -15918,13 +15918,13 @@
         <v>0</v>
       </c>
       <c r="L201" t="n">
-        <v>29.49999999999999</v>
+        <v>29.5</v>
       </c>
       <c r="M201" t="n">
         <v>19.5284</v>
       </c>
       <c r="N201" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="O201" t="n">
         <v>74.7364</v>
@@ -15933,7 +15933,7 @@
         <v>120</v>
       </c>
       <c r="Q201" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -16001,10 +16001,10 @@
         <v>24.5644</v>
       </c>
       <c r="N202" t="n">
-        <v>1.020304050607109</v>
+        <v>1.020304050607095</v>
       </c>
       <c r="O202" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P202" t="n">
         <v>121.010101010101</v>
@@ -16066,10 +16066,10 @@
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K203" t="n">
-        <v>130.2359183673469</v>
+        <v>128.7383415243649</v>
       </c>
       <c r="L203" t="n">
         <v>158.7359183673469</v>
@@ -16078,10 +16078,10 @@
         <v>18.1532</v>
       </c>
       <c r="N203" t="n">
-        <v>-2.87087974044485e-14</v>
+        <v>-7.177199351112124e-15</v>
       </c>
       <c r="O203" t="n">
-        <v>1</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="P203" t="n">
         <v>120</v>
@@ -16137,13 +16137,13 @@
         <v>27</v>
       </c>
       <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
         <v>27</v>
       </c>
-      <c r="I204" t="n">
-        <v>0</v>
-      </c>
       <c r="J204" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
@@ -16155,13 +16155,13 @@
         <v>18.1532</v>
       </c>
       <c r="N204" t="n">
-        <v>181.1134578104275</v>
+        <v>160.1131517192123</v>
       </c>
       <c r="O204" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P204" t="n">
-        <v>299.3023232323232</v>
+        <v>278.5120202020202</v>
       </c>
       <c r="Q204" t="n">
         <v>1</v>
@@ -16173,7 +16173,7 @@
         <v>0</v>
       </c>
       <c r="T204" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U204" t="n">
         <v>0</v>
@@ -16226,22 +16226,22 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>29.50000000000007</v>
+        <v>29.49999999999999</v>
       </c>
       <c r="M205" t="n">
         <v>19.8</v>
       </c>
       <c r="N205" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>2.870879740444849e-14</v>
       </c>
       <c r="O205" t="n">
-        <v>129.9769999999999</v>
+        <v>129.977</v>
       </c>
       <c r="P205" t="n">
-        <v>168.0124242424243</v>
+        <v>147.2221212121212</v>
       </c>
       <c r="Q205" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R205" t="n">
         <v>0</v>
@@ -16250,7 +16250,7 @@
         <v>0</v>
       </c>
       <c r="T205" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U205" t="n">
         <v>0</v>
@@ -16297,7 +16297,7 @@
         <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -16309,16 +16309,16 @@
         <v>22.7644</v>
       </c>
       <c r="N206" t="n">
-        <v>33.90918367347013</v>
+        <v>32.02020202020201</v>
       </c>
       <c r="O206" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P206" t="n">
-        <v>201.5825160791597</v>
+        <v>178.9221212121212</v>
       </c>
       <c r="Q206" t="n">
-        <v>1.000000000000001</v>
+        <v>1</v>
       </c>
       <c r="R206" t="n">
         <v>0</v>
@@ -16368,13 +16368,13 @@
         <v>36</v>
       </c>
       <c r="H207" t="n">
-        <v>36</v>
+        <v>5.520408163265282</v>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>30.47959183673472</v>
       </c>
       <c r="J207" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K207" t="n">
         <v>0</v>
@@ -16386,13 +16386,13 @@
         <v>22.7644</v>
       </c>
       <c r="N207" t="n">
-        <v>34.99999999999998</v>
+        <v>1.000000000000027</v>
       </c>
       <c r="O207" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P207" t="n">
-        <v>236.2325160791597</v>
+        <v>179.9121212121212</v>
       </c>
       <c r="Q207" t="n">
         <v>1</v>
@@ -16404,7 +16404,7 @@
         <v>0</v>
       </c>
       <c r="T207" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U207" t="n">
         <v>0</v>
@@ -16451,7 +16451,7 @@
         <v>0</v>
       </c>
       <c r="J208" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
@@ -16463,13 +16463,13 @@
         <v>21.4324</v>
       </c>
       <c r="N208" t="n">
-        <v>154.2766059791857</v>
+        <v>210.9880666071144</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
       </c>
       <c r="P208" t="n">
-        <v>388.9663559985535</v>
+        <v>388.7903071531645</v>
       </c>
       <c r="Q208" t="n">
         <v>1</v>
@@ -16481,7 +16481,7 @@
         <v>0</v>
       </c>
       <c r="T208" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U208" t="n">
         <v>0</v>
@@ -16496,7 +16496,7 @@
         <v>0</v>
       </c>
       <c r="Y208" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -16522,31 +16522,31 @@
         <v>45</v>
       </c>
       <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
         <v>45</v>
       </c>
-      <c r="I209" t="n">
-        <v>0</v>
-      </c>
       <c r="J209" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
       </c>
       <c r="L209" t="n">
-        <v>160.2775510204082</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M209" t="n">
         <v>16.628</v>
       </c>
       <c r="N209" t="n">
-        <v>600.0000000000001</v>
+        <v>586.4999999999997</v>
       </c>
       <c r="O209" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P209" t="n">
-        <v>982.9663559985536</v>
+        <v>969.4253071531641</v>
       </c>
       <c r="Q209" t="n">
         <v>1</v>
@@ -16558,7 +16558,7 @@
         <v>0</v>
       </c>
       <c r="T209" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U209" t="n">
         <v>0</v>
@@ -16567,7 +16567,7 @@
         <v>0</v>
       </c>
       <c r="W209" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X209" t="n">
         <v>0</v>
@@ -16599,34 +16599,34 @@
         <v>38.5</v>
       </c>
       <c r="H210" t="n">
-        <v>38.5</v>
+        <v>30.9039362913824</v>
       </c>
       <c r="I210" t="n">
-        <v>0</v>
+        <v>7.596063708617596</v>
       </c>
       <c r="J210" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>135.2571428571431</v>
+        <v>160.2775510204082</v>
       </c>
       <c r="M210" t="n">
         <v>16.628</v>
       </c>
       <c r="N210" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>29.8835281281171</v>
       </c>
       <c r="O210" t="n">
-        <v>24.51999999999982</v>
+        <v>5.275779813018744e-14</v>
       </c>
       <c r="P210" t="n">
-        <v>958.198679230877</v>
+        <v>999.01</v>
       </c>
       <c r="Q210" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="R210" t="n">
         <v>0</v>
@@ -16635,7 +16635,7 @@
         <v>0</v>
       </c>
       <c r="T210" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U210" t="n">
         <v>0</v>
@@ -16682,28 +16682,28 @@
         <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>131.2343856832601</v>
+        <v>145.214081632653</v>
       </c>
       <c r="M211" t="n">
         <v>19.5068</v>
       </c>
       <c r="N211" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>1</v>
       </c>
       <c r="O211" t="n">
-        <v>13.70010203040511</v>
+        <v>-9.01279051390702e-15</v>
       </c>
       <c r="P211" t="n">
-        <v>944.3601923314779</v>
+        <v>1000</v>
       </c>
       <c r="Q211" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="R211" t="n">
         <v>0</v>
@@ -16712,7 +16712,7 @@
         <v>0</v>
       </c>
       <c r="T211" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U211" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>85.39139999999999</v>
       </c>
       <c r="P212" t="n">
-        <v>858.1062529375386</v>
+        <v>913.7460606060606</v>
       </c>
       <c r="Q212" t="n">
         <v>-0</v>
@@ -16854,7 +16854,7 @@
         <v>100.5813999999999</v>
       </c>
       <c r="P213" t="n">
-        <v>756.5088792001649</v>
+        <v>812.1486868686869</v>
       </c>
       <c r="Q213" t="n">
         <v>-0</v>
@@ -16931,7 +16931,7 @@
         <v>124.504</v>
       </c>
       <c r="P214" t="n">
-        <v>630.7472630385487</v>
+        <v>686.3870707070707</v>
       </c>
       <c r="Q214" t="n">
         <v>-0</v>
@@ -17008,7 +17008,7 @@
         <v>119.983</v>
       </c>
       <c r="P215" t="n">
-        <v>509.5523135435992</v>
+        <v>565.1921212121213</v>
       </c>
       <c r="Q215" t="n">
         <v>-0</v>
@@ -17085,7 +17085,7 @@
         <v>121.453</v>
       </c>
       <c r="P216" t="n">
-        <v>386.8725155638011</v>
+        <v>442.5123232323233</v>
       </c>
       <c r="Q216" t="n">
         <v>-0</v>
@@ -17162,7 +17162,7 @@
         <v>111.5942</v>
       </c>
       <c r="P217" t="n">
-        <v>274.151101422387</v>
+        <v>329.7909090909092</v>
       </c>
       <c r="Q217" t="n">
         <v>-0</v>
@@ -17236,7 +17236,7 @@
         <v>121.2121212121212</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P218" t="n">
         <v>120</v>
@@ -17248,7 +17248,7 @@
         <v>0</v>
       </c>
       <c r="S218" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T218" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
         <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>56.40418160162752</v>
+        <v>56.40418160162748</v>
       </c>
       <c r="L219" t="n">
         <v>84.38387755102042</v>
@@ -17310,10 +17310,10 @@
         <v>14.1452</v>
       </c>
       <c r="N219" t="n">
-        <v>1.020304050607102</v>
+        <v>1.020304050607059</v>
       </c>
       <c r="O219" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P219" t="n">
         <v>121.010101010101</v>
@@ -17378,25 +17378,25 @@
         <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>56.36346938775507</v>
+        <v>56.3634693877551</v>
       </c>
       <c r="L220" t="n">
-        <v>83.36346938775509</v>
+        <v>83.3634693877551</v>
       </c>
       <c r="M220" t="n">
         <v>14.1452</v>
       </c>
       <c r="N220" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
-        <v>1.000000000000014</v>
+        <v>0.9999999999999982</v>
       </c>
       <c r="P220" t="n">
         <v>120</v>
       </c>
       <c r="Q220" t="n">
-        <v>-1.424642212178772e-14</v>
+        <v>0</v>
       </c>
       <c r="R220" t="n">
         <v>0</v>
@@ -17458,16 +17458,16 @@
         <v>353.4781576015775</v>
       </c>
       <c r="L221" t="n">
-        <v>85.42265306122451</v>
+        <v>85.42265306122449</v>
       </c>
       <c r="M221" t="n">
         <v>15.2312</v>
       </c>
       <c r="N221" t="n">
-        <v>298.055504540353</v>
+        <v>298.0555045403531</v>
       </c>
       <c r="O221" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="P221" t="n">
         <v>415.0749494949495</v>
@@ -17781,7 +17781,7 @@
         <v>120</v>
       </c>
       <c r="Q225" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R225" t="n">
         <v>0</v>
@@ -17843,16 +17843,16 @@
         <v>154.50744690775</v>
       </c>
       <c r="L226" t="n">
-        <v>153.4871428571428</v>
+        <v>153.4871428571429</v>
       </c>
       <c r="M226" t="n">
         <v>24.5644</v>
       </c>
       <c r="N226" t="n">
-        <v>1.020304050607124</v>
+        <v>1.020304050607096</v>
       </c>
       <c r="O226" t="n">
-        <v>2.813749233609997e-14</v>
+        <v>0</v>
       </c>
       <c r="P226" t="n">
         <v>121.010101010101</v>
@@ -17914,10 +17914,10 @@
         <v>0</v>
       </c>
       <c r="J227" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K227" t="n">
-        <v>158.7359183673469</v>
+        <v>157.2383415243649</v>
       </c>
       <c r="L227" t="n">
         <v>158.7359183673469</v>
@@ -17926,10 +17926,10 @@
         <v>18.1532</v>
       </c>
       <c r="N227" t="n">
-        <v>0</v>
+        <v>-1.332267629550188e-14</v>
       </c>
       <c r="O227" t="n">
-        <v>1.000000000000014</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="P227" t="n">
         <v>120</v>
@@ -17991,7 +17991,7 @@
         <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -18003,13 +18003,13 @@
         <v>18.1532</v>
       </c>
       <c r="N228" t="n">
-        <v>154.1134578104276</v>
+        <v>160.1131517192124</v>
       </c>
       <c r="O228" t="n">
         <v>0</v>
       </c>
       <c r="P228" t="n">
-        <v>272.5723232323233</v>
+        <v>278.5120202020203</v>
       </c>
       <c r="Q228" t="n">
         <v>1</v>
@@ -18071,25 +18071,25 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>7.500408163265211</v>
+        <v>1.500102040816274</v>
       </c>
       <c r="L229" t="n">
-        <v>8.000408163265341</v>
+        <v>2.000102040816245</v>
       </c>
       <c r="M229" t="n">
         <v>19.8</v>
       </c>
       <c r="N229" t="n">
-        <v>-1.296740492762183e-13</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="O229" t="n">
-        <v>151.0465999999999</v>
+        <v>156.9269000000001</v>
       </c>
       <c r="P229" t="n">
         <v>120</v>
       </c>
       <c r="Q229" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R229" t="n">
         <v>0</v>
@@ -18145,7 +18145,7 @@
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
@@ -18157,13 +18157,13 @@
         <v>22.7644</v>
       </c>
       <c r="N230" t="n">
-        <v>8.90918367347013</v>
+        <v>7.020202020202041</v>
       </c>
       <c r="O230" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P230" t="n">
-        <v>128.8200918367354</v>
+        <v>126.95</v>
       </c>
       <c r="Q230" t="n">
         <v>1</v>
@@ -18175,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="T230" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U230" t="n">
         <v>0</v>
@@ -18216,13 +18216,13 @@
         <v>24</v>
       </c>
       <c r="H231" t="n">
-        <v>24</v>
+        <v>21.42143658810344</v>
       </c>
       <c r="I231" t="n">
-        <v>0</v>
+        <v>2.57856341189656</v>
       </c>
       <c r="J231" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
@@ -18234,13 +18234,13 @@
         <v>22.7644</v>
       </c>
       <c r="N231" t="n">
-        <v>22.99999999999998</v>
+        <v>16.90102842483815</v>
       </c>
       <c r="O231" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P231" t="n">
-        <v>151.5900918367354</v>
+        <v>143.6820181405897</v>
       </c>
       <c r="Q231" t="n">
         <v>1</v>
@@ -18299,7 +18299,7 @@
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -18311,13 +18311,13 @@
         <v>21.4324</v>
       </c>
       <c r="N232" t="n">
-        <v>140.2766059791857</v>
+        <v>196.9880666071145</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
       </c>
       <c r="P232" t="n">
-        <v>290.4639317561292</v>
+        <v>338.700204081633</v>
       </c>
       <c r="Q232" t="n">
         <v>1</v>
@@ -18344,7 +18344,7 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -18370,31 +18370,31 @@
         <v>40</v>
       </c>
       <c r="H233" t="n">
-        <v>40</v>
+        <v>13.5000000000004</v>
       </c>
       <c r="I233" t="n">
-        <v>0</v>
+        <v>26.4999999999996</v>
       </c>
       <c r="J233" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>160.2775510204082</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M233" t="n">
         <v>16.628</v>
       </c>
       <c r="N233" t="n">
-        <v>594.9999999999999</v>
+        <v>599.9999999999999</v>
       </c>
       <c r="O233" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P233" t="n">
-        <v>879.5139317561292</v>
+        <v>932.7002040816329</v>
       </c>
       <c r="Q233" t="n">
         <v>1</v>
@@ -18406,7 +18406,7 @@
         <v>0</v>
       </c>
       <c r="T233" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U233" t="n">
         <v>0</v>
@@ -18415,7 +18415,7 @@
         <v>0</v>
       </c>
       <c r="W233" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X233" t="n">
         <v>0</v>
@@ -18453,28 +18453,28 @@
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K234" t="n">
         <v>0</v>
       </c>
       <c r="L234" t="n">
-        <v>146.2571428571425</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M234" t="n">
         <v>16.628</v>
       </c>
       <c r="N234" t="n">
-        <v>6.764510388423176e-13</v>
+        <v>48.47959183673471</v>
       </c>
       <c r="O234" t="n">
-        <v>13.74000000000032</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P234" t="n">
-        <v>865.6351438773416</v>
+        <v>980.6950000000003</v>
       </c>
       <c r="Q234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R234" t="n">
         <v>0</v>
@@ -18492,7 +18492,7 @@
         <v>0</v>
       </c>
       <c r="W234" t="n">
-        <v>41.57</v>
+        <v>41.56999999999999</v>
       </c>
       <c r="X234" t="n">
         <v>0</v>
@@ -18530,7 +18530,7 @@
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -18542,13 +18542,13 @@
         <v>19.5068</v>
       </c>
       <c r="N235" t="n">
-        <v>4.520304050607142</v>
+        <v>19.49999999999972</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
       </c>
       <c r="P235" t="n">
-        <v>870.1102448874427</v>
+        <v>1000</v>
       </c>
       <c r="Q235" t="n">
         <v>1</v>
@@ -18613,19 +18613,19 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>64</v>
+        <v>64.00000000000006</v>
       </c>
       <c r="M236" t="n">
         <v>17.2364</v>
       </c>
       <c r="N236" t="n">
-        <v>7.177199351112125e-15</v>
+        <v>-1.507211863733546e-13</v>
       </c>
       <c r="O236" t="n">
-        <v>72.16139999999999</v>
+        <v>72.16139999999994</v>
       </c>
       <c r="P236" t="n">
-        <v>797.2199418571397</v>
+        <v>927.1096969696969</v>
       </c>
       <c r="Q236" t="n">
         <v>-0</v>
@@ -18690,19 +18690,19 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>40.99999999999996</v>
+        <v>40.99999999999994</v>
       </c>
       <c r="M237" t="n">
         <v>17.2364</v>
       </c>
       <c r="N237" t="n">
-        <v>2.153159805333637e-14</v>
+        <v>-5.024039545778486e-14</v>
       </c>
       <c r="O237" t="n">
-        <v>94.70140000000002</v>
+        <v>94.70140000000006</v>
       </c>
       <c r="P237" t="n">
-        <v>701.5619620591599</v>
+        <v>831.451717171717</v>
       </c>
       <c r="Q237" t="n">
         <v>-0</v>
@@ -18779,7 +18779,7 @@
         <v>124.504</v>
       </c>
       <c r="P238" t="n">
-        <v>575.8003458975437</v>
+        <v>705.6901010101008</v>
       </c>
       <c r="Q238" t="n">
         <v>-0</v>
@@ -18856,7 +18856,7 @@
         <v>118.023</v>
       </c>
       <c r="P239" t="n">
-        <v>456.5851943823922</v>
+        <v>586.4749494949492</v>
       </c>
       <c r="Q239" t="n">
         <v>-0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="O240" t="n">
-        <v>119.003</v>
+        <v>119.0029999999999</v>
       </c>
       <c r="P240" t="n">
-        <v>336.3801438773417</v>
+        <v>466.2698989898988</v>
       </c>
       <c r="Q240" t="n">
         <v>-0</v>
@@ -19010,7 +19010,7 @@
         <v>109.6342</v>
       </c>
       <c r="P241" t="n">
-        <v>225.6385277157255</v>
+        <v>355.5282828282826</v>
       </c>
       <c r="Q241" t="n">
         <v>-0</v>
@@ -19037,7 +19037,7 @@
         <v>0</v>
       </c>
       <c r="Y241" t="n">
-        <v>0.9999999999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -19051,7 +19051,7 @@
         <v>1</v>
       </c>
       <c r="D242" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E242" t="n">
         <v>35.363</v>
@@ -19072,10 +19072,10 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>191.8337538651824</v>
+        <v>192.5959987631416</v>
       </c>
       <c r="L242" t="n">
-        <v>83.62163265306123</v>
+        <v>84.38387755102042</v>
       </c>
       <c r="M242" t="n">
         <v>14.1452</v>
@@ -19084,7 +19084,7 @@
         <v>121.2121212121212</v>
       </c>
       <c r="O242" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P242" t="n">
         <v>120</v>
@@ -19128,7 +19128,7 @@
         <v>2</v>
       </c>
       <c r="D243" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E243" t="n">
         <v>35.363</v>
@@ -19149,19 +19149,19 @@
         <v>0</v>
       </c>
       <c r="K243" t="n">
-        <v>72.14193670366832</v>
+        <v>72.90418160162747</v>
       </c>
       <c r="L243" t="n">
-        <v>83.62163265306123</v>
+        <v>84.38387755102039</v>
       </c>
       <c r="M243" t="n">
         <v>14.1452</v>
       </c>
       <c r="N243" t="n">
-        <v>1.020304050607095</v>
+        <v>1.020304050607081</v>
       </c>
       <c r="O243" t="n">
-        <v>1.340927369142264e-14</v>
+        <v>2.747801985947262e-14</v>
       </c>
       <c r="P243" t="n">
         <v>121.010101010101</v>
@@ -19205,7 +19205,7 @@
         <v>3</v>
       </c>
       <c r="D244" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E244" t="n">
         <v>35.363</v>
@@ -19226,10 +19226,10 @@
         <v>0</v>
       </c>
       <c r="K244" t="n">
-        <v>69.60122448979592</v>
+        <v>70.3634693877551</v>
       </c>
       <c r="L244" t="n">
-        <v>82.60122448979592</v>
+        <v>83.3634693877551</v>
       </c>
       <c r="M244" t="n">
         <v>14.1452</v>
@@ -19238,7 +19238,7 @@
         <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>1</v>
+        <v>0.9999999999999982</v>
       </c>
       <c r="P244" t="n">
         <v>120</v>
@@ -19282,7 +19282,7 @@
         <v>4</v>
       </c>
       <c r="D245" t="n">
-        <v>67.804</v>
+        <v>68.483</v>
       </c>
       <c r="E245" t="n">
         <v>38.078</v>
@@ -19303,16 +19303,16 @@
         <v>0</v>
       </c>
       <c r="K245" t="n">
-        <v>68.72979591836736</v>
+        <v>69.42265306122448</v>
       </c>
       <c r="L245" t="n">
-        <v>84.72979591836736</v>
+        <v>85.42265306122449</v>
       </c>
       <c r="M245" t="n">
         <v>15.2312</v>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>0.9999999999999858</v>
       </c>
       <c r="O245" t="n">
         <v>0</v>
@@ -19359,7 +19359,7 @@
         <v>5</v>
       </c>
       <c r="D246" t="n">
-        <v>67.804</v>
+        <v>68.483</v>
       </c>
       <c r="E246" t="n">
         <v>38.078</v>
@@ -19380,25 +19380,25 @@
         <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>332.0522119983593</v>
+        <v>344.057180150297</v>
       </c>
       <c r="L246" t="n">
-        <v>84.72979591836739</v>
+        <v>85.42265306122431</v>
       </c>
       <c r="M246" t="n">
         <v>15.2312</v>
       </c>
       <c r="N246" t="n">
-        <v>269.3224160799919</v>
+        <v>280.6345270890727</v>
       </c>
       <c r="O246" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>1.84741111297626e-13</v>
       </c>
       <c r="P246" t="n">
-        <v>387.619191919192</v>
+        <v>398.8181818181819</v>
       </c>
       <c r="Q246" t="n">
-        <v>1</v>
+        <v>0.9999999999999991</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
@@ -19436,7 +19436,7 @@
         <v>6</v>
       </c>
       <c r="D247" t="n">
-        <v>75.039</v>
+        <v>75.066</v>
       </c>
       <c r="E247" t="n">
         <v>38.078</v>
@@ -19469,13 +19469,13 @@
         <v>0</v>
       </c>
       <c r="O247" t="n">
-        <v>74.59020000000001</v>
+        <v>74.6172</v>
       </c>
       <c r="P247" t="n">
-        <v>312.2755555555556</v>
+        <v>323.4472727272728</v>
       </c>
       <c r="Q247" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
@@ -19513,7 +19513,7 @@
         <v>7</v>
       </c>
       <c r="D248" t="n">
-        <v>78.58799999999999</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E248" t="n">
         <v>48.821</v>
@@ -19537,22 +19537,22 @@
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>4.999999999999999</v>
+        <v>5</v>
       </c>
       <c r="M248" t="n">
         <v>19.5284</v>
       </c>
       <c r="N248" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="O248" t="n">
-        <v>93.21639999999999</v>
+        <v>98.74639999999999</v>
       </c>
       <c r="P248" t="n">
-        <v>218.1175757575758</v>
+        <v>223.7034343434344</v>
       </c>
       <c r="Q248" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R248" t="n">
         <v>0</v>
@@ -19590,7 +19590,7 @@
         <v>8</v>
       </c>
       <c r="D249" t="n">
-        <v>78.58799999999999</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E249" t="n">
         <v>48.821</v>
@@ -19623,7 +19623,7 @@
         <v>0</v>
       </c>
       <c r="O249" t="n">
-        <v>97.13639999999999</v>
+        <v>102.6664</v>
       </c>
       <c r="P249" t="n">
         <v>120</v>
@@ -19667,7 +19667,7 @@
         <v>9</v>
       </c>
       <c r="D250" t="n">
-        <v>118.618</v>
+        <v>125.853</v>
       </c>
       <c r="E250" t="n">
         <v>61.411</v>
@@ -19688,22 +19688,22 @@
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>146.6247938465255</v>
+        <v>154.0074469077499</v>
       </c>
       <c r="L250" t="n">
-        <v>146.1044897959184</v>
+        <v>153.4871428571429</v>
       </c>
       <c r="M250" t="n">
         <v>24.5644</v>
       </c>
       <c r="N250" t="n">
-        <v>1.020304050607137</v>
+        <v>1.020304050607081</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P250" t="n">
-        <v>121.0101010101011</v>
+        <v>121.010101010101</v>
       </c>
       <c r="Q250" t="n">
         <v>1</v>
@@ -19744,7 +19744,7 @@
         <v>10</v>
       </c>
       <c r="D251" t="n">
-        <v>116.928</v>
+        <v>138.408</v>
       </c>
       <c r="E251" t="n">
         <v>45.383</v>
@@ -19762,28 +19762,28 @@
         <v>0</v>
       </c>
       <c r="J251" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K251" t="n">
-        <v>135.8175510204081</v>
+        <v>156.2383415243649</v>
       </c>
       <c r="L251" t="n">
-        <v>136.8175510204081</v>
+        <v>158.7359183673469</v>
       </c>
       <c r="M251" t="n">
         <v>18.1532</v>
       </c>
       <c r="N251" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>-7.177199351112124e-15</v>
       </c>
       <c r="O251" t="n">
-        <v>1.000000000000028</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="P251" t="n">
         <v>120</v>
       </c>
       <c r="Q251" t="n">
-        <v>-2.047872692314812e-14</v>
+        <v>0</v>
       </c>
       <c r="R251" t="n">
         <v>0</v>
@@ -19821,7 +19821,7 @@
         <v>11</v>
       </c>
       <c r="D252" t="n">
-        <v>116.928</v>
+        <v>138.408</v>
       </c>
       <c r="E252" t="n">
         <v>45.383</v>
@@ -19839,25 +19839,25 @@
         <v>2</v>
       </c>
       <c r="J252" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>137.8379591836735</v>
+        <v>159.7563265306122</v>
       </c>
       <c r="M252" t="n">
         <v>18.1532</v>
       </c>
       <c r="N252" t="n">
-        <v>176.0318251573663</v>
+        <v>160.1131517192124</v>
       </c>
       <c r="O252" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P252" t="n">
-        <v>294.2715069057926</v>
+        <v>278.5120202020203</v>
       </c>
       <c r="Q252" t="n">
         <v>1</v>
@@ -19869,7 +19869,7 @@
         <v>0</v>
       </c>
       <c r="T252" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U252" t="n">
         <v>0</v>
@@ -19898,7 +19898,7 @@
         <v>12</v>
       </c>
       <c r="D253" t="n">
-        <v>115.137</v>
+        <v>139.087</v>
       </c>
       <c r="E253" t="n">
         <v>49.5</v>
@@ -19928,13 +19928,13 @@
         <v>19.8</v>
       </c>
       <c r="N253" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>127.587</v>
+        <v>151.537</v>
       </c>
       <c r="P253" t="n">
-        <v>165.395749330035</v>
+        <v>125.4443434343435</v>
       </c>
       <c r="Q253" t="n">
         <v>0</v>
@@ -19946,7 +19946,7 @@
         <v>0</v>
       </c>
       <c r="T253" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U253" t="n">
         <v>0</v>
@@ -19975,7 +19975,7 @@
         <v>13</v>
       </c>
       <c r="D254" t="n">
-        <v>112.44</v>
+        <v>136.236</v>
       </c>
       <c r="E254" t="n">
         <v>56.911</v>
@@ -19987,31 +19987,31 @@
         <v>33.5</v>
       </c>
       <c r="H254" t="n">
-        <v>0</v>
+        <v>0.47979797979797</v>
       </c>
       <c r="I254" t="n">
-        <v>33.5</v>
+        <v>33.02020202020203</v>
       </c>
       <c r="J254" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
       </c>
       <c r="L254" t="n">
-        <v>137.9636734693877</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M254" t="n">
         <v>22.7644</v>
       </c>
       <c r="N254" t="n">
-        <v>26.69081632653142</v>
+        <v>1.000000000000002</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P254" t="n">
-        <v>191.8196574933012</v>
+        <v>126.4343434343435</v>
       </c>
       <c r="Q254" t="n">
         <v>1</v>
@@ -20052,7 +20052,7 @@
         <v>14</v>
       </c>
       <c r="D255" t="n">
-        <v>112.44</v>
+        <v>136.236</v>
       </c>
       <c r="E255" t="n">
         <v>56.911</v>
@@ -20064,31 +20064,31 @@
         <v>46</v>
       </c>
       <c r="H255" t="n">
-        <v>0</v>
+        <v>5.520408163265288</v>
       </c>
       <c r="I255" t="n">
-        <v>46</v>
+        <v>40.47959183673471</v>
       </c>
       <c r="J255" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K255" t="n">
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>137.9636734693878</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M255" t="n">
         <v>22.7644</v>
       </c>
       <c r="N255" t="n">
-        <v>23.28163265306119</v>
+        <v>0.9999999999999867</v>
       </c>
       <c r="O255" t="n">
-        <v>2.462030579408747e-14</v>
+        <v>6.045164369083977e-15</v>
       </c>
       <c r="P255" t="n">
-        <v>214.8684738198317</v>
+        <v>127.4243434343435</v>
       </c>
       <c r="Q255" t="n">
         <v>1</v>
@@ -20129,7 +20129,7 @@
         <v>15</v>
       </c>
       <c r="D256" t="n">
-        <v>114.258</v>
+        <v>122.799</v>
       </c>
       <c r="E256" t="n">
         <v>53.581</v>
@@ -20147,28 +20147,28 @@
         <v>60</v>
       </c>
       <c r="J256" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>138.4595918367347</v>
+        <v>147.1748979591837</v>
       </c>
       <c r="M256" t="n">
         <v>21.4324</v>
       </c>
       <c r="N256" t="n">
-        <v>116.4919121016347</v>
+        <v>164.4880666071145</v>
       </c>
       <c r="O256" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="P256" t="n">
-        <v>330.19546680045</v>
+        <v>290.2675293753869</v>
       </c>
       <c r="Q256" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R256" t="n">
         <v>0</v>
@@ -20177,7 +20177,7 @@
         <v>0</v>
       </c>
       <c r="T256" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U256" t="n">
         <v>0</v>
@@ -20206,7 +20206,7 @@
         <v>16</v>
       </c>
       <c r="D257" t="n">
-        <v>131.363</v>
+        <v>140.444</v>
       </c>
       <c r="E257" t="n">
         <v>41.57</v>
@@ -20218,31 +20218,31 @@
         <v>77.5</v>
       </c>
       <c r="H257" t="n">
-        <v>17.73258456571784</v>
+        <v>0</v>
       </c>
       <c r="I257" t="n">
-        <v>59.76741543428216</v>
+        <v>77.5</v>
       </c>
       <c r="J257" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>151.011224489796</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M257" t="n">
         <v>16.628</v>
       </c>
       <c r="N257" t="n">
-        <v>581.9989110963302</v>
+        <v>586.4999999999998</v>
       </c>
       <c r="O257" t="n">
-        <v>0</v>
+        <v>2.250999386887997e-13</v>
       </c>
       <c r="P257" t="n">
-        <v>906.3743887858169</v>
+        <v>870.9025293753864</v>
       </c>
       <c r="Q257" t="n">
         <v>1</v>
@@ -20254,7 +20254,7 @@
         <v>0</v>
       </c>
       <c r="T257" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U257" t="n">
         <v>0</v>
@@ -20283,7 +20283,7 @@
         <v>17</v>
       </c>
       <c r="D258" t="n">
-        <v>131.363</v>
+        <v>140.444</v>
       </c>
       <c r="E258" t="n">
         <v>41.57</v>
@@ -20295,31 +20295,31 @@
         <v>90</v>
       </c>
       <c r="H258" t="n">
-        <v>90</v>
+        <v>86.4218936426733</v>
       </c>
       <c r="I258" t="n">
-        <v>0</v>
+        <v>3.578106357326703</v>
       </c>
       <c r="J258" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K258" t="n">
         <v>0</v>
       </c>
       <c r="L258" t="n">
-        <v>151.0112244897958</v>
+        <v>160.2775510204082</v>
       </c>
       <c r="M258" t="n">
         <v>16.628</v>
       </c>
       <c r="N258" t="n">
-        <v>35.74591836734734</v>
+        <v>85.401485479408</v>
       </c>
       <c r="O258" t="n">
-        <v>-1.899280732686748e-13</v>
+        <v>2.813749233609997e-14</v>
       </c>
       <c r="P258" t="n">
-        <v>941.762847969491</v>
+        <v>955.4500000000003</v>
       </c>
       <c r="Q258" t="n">
         <v>1</v>
@@ -20360,7 +20360,7 @@
         <v>18</v>
       </c>
       <c r="D259" t="n">
-        <v>94.574</v>
+        <v>122.803</v>
       </c>
       <c r="E259" t="n">
         <v>48.767</v>
@@ -20378,28 +20378,28 @@
         <v>0</v>
       </c>
       <c r="J259" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
       </c>
       <c r="L259" t="n">
-        <v>116.4089795918367</v>
+        <v>145.2140816326533</v>
       </c>
       <c r="M259" t="n">
         <v>19.5068</v>
       </c>
       <c r="N259" t="n">
-        <v>58.82540609142342</v>
+        <v>44.99999999999972</v>
       </c>
       <c r="O259" t="n">
-        <v>1.406874616804998e-13</v>
+        <v>-7.034373084024992e-15</v>
       </c>
       <c r="P259" t="n">
         <v>1000</v>
       </c>
       <c r="Q259" t="n">
-        <v>1</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="R259" t="n">
         <v>0</v>
@@ -20408,7 +20408,7 @@
         <v>0</v>
       </c>
       <c r="T259" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U259" t="n">
         <v>0</v>
@@ -20437,7 +20437,7 @@
         <v>19</v>
       </c>
       <c r="D260" t="n">
-        <v>91.65600000000001</v>
+        <v>117.645</v>
       </c>
       <c r="E260" t="n">
         <v>43.091</v>
@@ -20461,19 +20461,19 @@
         <v>0</v>
       </c>
       <c r="L260" t="n">
-        <v>64.50000000000001</v>
+        <v>64.50000000000003</v>
       </c>
       <c r="M260" t="n">
         <v>17.2364</v>
       </c>
       <c r="N260" t="n">
-        <v>5.024039545778486e-14</v>
+        <v>2.870879740444849e-14</v>
       </c>
       <c r="O260" t="n">
-        <v>45.68239999999999</v>
+        <v>71.67139999999996</v>
       </c>
       <c r="P260" t="n">
-        <v>953.8561616161617</v>
+        <v>927.6046464646465</v>
       </c>
       <c r="Q260" t="n">
         <v>-0</v>
@@ -20485,7 +20485,7 @@
         <v>0</v>
       </c>
       <c r="T260" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U260" t="n">
         <v>0</v>
@@ -20500,7 +20500,7 @@
         <v>0</v>
       </c>
       <c r="Y260" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -20514,7 +20514,7 @@
         <v>20</v>
       </c>
       <c r="D261" t="n">
-        <v>91.65600000000001</v>
+        <v>117.645</v>
       </c>
       <c r="E261" t="n">
         <v>43.091</v>
@@ -20544,13 +20544,13 @@
         <v>17.2364</v>
       </c>
       <c r="N261" t="n">
-        <v>-9.33035915644576e-14</v>
+        <v>2.153159805333637e-14</v>
       </c>
       <c r="O261" t="n">
-        <v>86.84240000000001</v>
+        <v>112.8314</v>
       </c>
       <c r="P261" t="n">
-        <v>866.1365656565656</v>
+        <v>813.6335353535354</v>
       </c>
       <c r="Q261" t="n">
         <v>-0</v>
@@ -20591,7 +20591,7 @@
         <v>21</v>
       </c>
       <c r="D262" t="n">
-        <v>93.696</v>
+        <v>119.884</v>
       </c>
       <c r="E262" t="n">
         <v>44.625</v>
@@ -20624,10 +20624,10 @@
         <v>0</v>
       </c>
       <c r="O262" t="n">
-        <v>103.706</v>
+        <v>129.894</v>
       </c>
       <c r="P262" t="n">
-        <v>761.3830303030303</v>
+        <v>682.4274747474748</v>
       </c>
       <c r="Q262" t="n">
         <v>-0</v>
@@ -20668,7 +20668,7 @@
         <v>22</v>
       </c>
       <c r="D263" t="n">
-        <v>98.786</v>
+        <v>110.043</v>
       </c>
       <c r="E263" t="n">
         <v>40.775</v>
@@ -20698,16 +20698,16 @@
         <v>16.31</v>
       </c>
       <c r="N263" t="n">
-        <v>-8.612639221334548e-14</v>
+        <v>-1.291895883200182e-13</v>
       </c>
       <c r="O263" t="n">
-        <v>85.696</v>
+        <v>96.953</v>
       </c>
       <c r="P263" t="n">
-        <v>674.821414141414</v>
+        <v>584.4951515151514</v>
       </c>
       <c r="Q263" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R263" t="n">
         <v>0</v>
@@ -20716,7 +20716,7 @@
         <v>0</v>
       </c>
       <c r="T263" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U263" t="n">
         <v>0</v>
@@ -20745,7 +20745,7 @@
         <v>23</v>
       </c>
       <c r="D264" t="n">
-        <v>98.786</v>
+        <v>110.043</v>
       </c>
       <c r="E264" t="n">
         <v>40.775</v>
@@ -20769,19 +20769,19 @@
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>46.5</v>
+        <v>46.49999999999997</v>
       </c>
       <c r="M264" t="n">
         <v>16.31</v>
       </c>
       <c r="N264" t="n">
-        <v>0</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="O264" t="n">
-        <v>69.52600000000001</v>
+        <v>80.78300000000003</v>
       </c>
       <c r="P264" t="n">
-        <v>604.5931313131312</v>
+        <v>502.8961616161615</v>
       </c>
       <c r="Q264" t="n">
         <v>-0</v>
@@ -20822,7 +20822,7 @@
         <v>24</v>
       </c>
       <c r="D265" t="n">
-        <v>97.666</v>
+        <v>102.145</v>
       </c>
       <c r="E265" t="n">
         <v>34.648</v>
@@ -20855,10 +20855,10 @@
         <v>0</v>
       </c>
       <c r="O265" t="n">
-        <v>76.73519999999999</v>
+        <v>81.21420000000001</v>
       </c>
       <c r="P265" t="n">
-        <v>527.0828282828281</v>
+        <v>420.8616161616161</v>
       </c>
       <c r="Q265" t="n">
         <v>-0</v>
@@ -20870,7 +20870,7 @@
         <v>0</v>
       </c>
       <c r="T265" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U265" t="n">
         <v>0</v>
@@ -20885,7 +20885,7 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>0.9999999999999993</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -20899,7 +20899,7 @@
         <v>1</v>
       </c>
       <c r="D266" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E266" t="n">
         <v>35.363</v>
@@ -20920,10 +20920,10 @@
         <v>0</v>
       </c>
       <c r="K266" t="n">
-        <v>192.8337538651824</v>
+        <v>193.5959987631416</v>
       </c>
       <c r="L266" t="n">
-        <v>83.62163265306123</v>
+        <v>84.38387755102042</v>
       </c>
       <c r="M266" t="n">
         <v>14.1452</v>
@@ -20932,7 +20932,7 @@
         <v>121.2121212121212</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P266" t="n">
         <v>120</v>
@@ -20944,7 +20944,7 @@
         <v>0</v>
       </c>
       <c r="S266" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T266" t="n">
         <v>0</v>
@@ -20976,7 +20976,7 @@
         <v>2</v>
       </c>
       <c r="D267" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E267" t="n">
         <v>35.363</v>
@@ -20997,22 +20997,22 @@
         <v>0</v>
       </c>
       <c r="K267" t="n">
-        <v>126.2370290411849</v>
+        <v>127.7614410649476</v>
       </c>
       <c r="L267" t="n">
-        <v>83.62163265306123</v>
+        <v>84.38387755102042</v>
       </c>
       <c r="M267" t="n">
         <v>14.1452</v>
       </c>
       <c r="N267" t="n">
-        <v>61.11539638812366</v>
+        <v>61.87756351392716</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="P267" t="n">
-        <v>180.5042424242424</v>
+        <v>181.2587878787879</v>
       </c>
       <c r="Q267" t="n">
         <v>1</v>
@@ -21053,7 +21053,7 @@
         <v>3</v>
       </c>
       <c r="D268" t="n">
-        <v>67.804</v>
+        <v>68.551</v>
       </c>
       <c r="E268" t="n">
         <v>35.363</v>
@@ -21077,22 +21077,22 @@
         <v>0</v>
       </c>
       <c r="L268" t="n">
-        <v>22.49999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="M268" t="n">
         <v>14.1452</v>
       </c>
       <c r="N268" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
-        <v>59.89920000000002</v>
+        <v>60.6462</v>
       </c>
       <c r="P268" t="n">
         <v>120</v>
       </c>
       <c r="Q268" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R268" t="n">
         <v>0</v>
@@ -21130,7 +21130,7 @@
         <v>4</v>
       </c>
       <c r="D269" t="n">
-        <v>67.804</v>
+        <v>68.483</v>
       </c>
       <c r="E269" t="n">
         <v>38.078</v>
@@ -21151,25 +21151,25 @@
         <v>0</v>
       </c>
       <c r="K269" t="n">
-        <v>111.9540587486908</v>
+        <v>113.3397023419101</v>
       </c>
       <c r="L269" t="n">
-        <v>84.72979591836737</v>
+        <v>85.42265306122449</v>
       </c>
       <c r="M269" t="n">
         <v>15.2312</v>
       </c>
       <c r="N269" t="n">
-        <v>54.22426283032341</v>
+        <v>54.91704928068565</v>
       </c>
       <c r="O269" t="n">
-        <v>-2.110311925207497e-14</v>
+        <v>-7.034373084024992e-15</v>
       </c>
       <c r="P269" t="n">
-        <v>173.6820202020202</v>
+        <v>174.3678787878788</v>
       </c>
       <c r="Q269" t="n">
-        <v>0.9999999999999998</v>
+        <v>1</v>
       </c>
       <c r="R269" t="n">
         <v>0</v>
@@ -21207,7 +21207,7 @@
         <v>5</v>
       </c>
       <c r="D270" t="n">
-        <v>67.804</v>
+        <v>68.483</v>
       </c>
       <c r="E270" t="n">
         <v>38.078</v>
@@ -21237,16 +21237,16 @@
         <v>15.2312</v>
       </c>
       <c r="N270" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>0</v>
       </c>
       <c r="O270" t="n">
-        <v>53.1452</v>
+        <v>53.8242</v>
       </c>
       <c r="P270" t="n">
         <v>120</v>
       </c>
       <c r="Q270" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R270" t="n">
         <v>0</v>
@@ -21284,7 +21284,7 @@
         <v>6</v>
       </c>
       <c r="D271" t="n">
-        <v>75.039</v>
+        <v>75.066</v>
       </c>
       <c r="E271" t="n">
         <v>38.078</v>
@@ -21305,22 +21305,22 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
-        <v>239.3328856697255</v>
+        <v>250.644999489848</v>
       </c>
       <c r="L271" t="n">
-        <v>92.11244897959179</v>
+        <v>92.13999999999997</v>
       </c>
       <c r="M271" t="n">
         <v>15.2312</v>
       </c>
       <c r="N271" t="n">
-        <v>167.7204366901337</v>
+        <v>179.004999489848</v>
       </c>
       <c r="O271" t="n">
-        <v>2.813749233609997e-14</v>
+        <v>0</v>
       </c>
       <c r="P271" t="n">
-        <v>286.0432323232323</v>
+        <v>297.2149494949495</v>
       </c>
       <c r="Q271" t="n">
         <v>1</v>
@@ -21361,7 +21361,7 @@
         <v>7</v>
       </c>
       <c r="D272" t="n">
-        <v>78.58799999999999</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E272" t="n">
         <v>48.821</v>
@@ -21394,10 +21394,10 @@
         <v>0</v>
       </c>
       <c r="O272" t="n">
-        <v>80.96639999999999</v>
+        <v>86.49640000000001</v>
       </c>
       <c r="P272" t="n">
-        <v>204.2589898989899</v>
+        <v>209.8448484848485</v>
       </c>
       <c r="Q272" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
         <v>8</v>
       </c>
       <c r="D273" t="n">
-        <v>78.58799999999999</v>
+        <v>84.11799999999999</v>
       </c>
       <c r="E273" t="n">
         <v>48.821</v>
@@ -21471,7 +21471,7 @@
         <v>0</v>
       </c>
       <c r="O273" t="n">
-        <v>83.41639999999998</v>
+        <v>88.9464</v>
       </c>
       <c r="P273" t="n">
         <v>120</v>
@@ -21515,7 +21515,7 @@
         <v>9</v>
       </c>
       <c r="D274" t="n">
-        <v>118.618</v>
+        <v>125.853</v>
       </c>
       <c r="E274" t="n">
         <v>61.411</v>
@@ -21536,19 +21536,19 @@
         <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>137.1247938465254</v>
+        <v>144.5074469077499</v>
       </c>
       <c r="L274" t="n">
-        <v>146.1044897959184</v>
+        <v>153.4871428571429</v>
       </c>
       <c r="M274" t="n">
         <v>24.5644</v>
       </c>
       <c r="N274" t="n">
-        <v>1.02030405060711</v>
+        <v>1.020304050607106</v>
       </c>
       <c r="O274" t="n">
-        <v>0</v>
+        <v>1.06581410364015e-14</v>
       </c>
       <c r="P274" t="n">
         <v>121.010101010101</v>
@@ -21592,7 +21592,7 @@
         <v>10</v>
       </c>
       <c r="D275" t="n">
-        <v>116.928</v>
+        <v>138.408</v>
       </c>
       <c r="E275" t="n">
         <v>45.383</v>
@@ -21610,22 +21610,22 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="K275" t="n">
-        <v>133.8175510204082</v>
+        <v>154.2383415243649</v>
       </c>
       <c r="L275" t="n">
-        <v>136.8175510204082</v>
+        <v>158.7359183673469</v>
       </c>
       <c r="M275" t="n">
         <v>18.1532</v>
       </c>
       <c r="N275" t="n">
-        <v>-2.870879740444849e-14</v>
+        <v>-7.177199351112124e-15</v>
       </c>
       <c r="O275" t="n">
-        <v>1</v>
+        <v>1.000000000000004</v>
       </c>
       <c r="P275" t="n">
         <v>120</v>
@@ -21669,7 +21669,7 @@
         <v>11</v>
       </c>
       <c r="D276" t="n">
-        <v>116.928</v>
+        <v>138.408</v>
       </c>
       <c r="E276" t="n">
         <v>45.383</v>
@@ -21687,25 +21687,25 @@
         <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>137.8379591836735</v>
+        <v>159.7563265306122</v>
       </c>
       <c r="M276" t="n">
         <v>18.1532</v>
       </c>
       <c r="N276" t="n">
-        <v>177.0318251573663</v>
+        <v>161.1131517192123</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="P276" t="n">
-        <v>295.2615069057926</v>
+        <v>279.5020202020202</v>
       </c>
       <c r="Q276" t="n">
         <v>1</v>
@@ -21714,7 +21714,7 @@
         <v>0</v>
       </c>
       <c r="S276" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T276" t="n">
         <v>0</v>
@@ -21746,7 +21746,7 @@
         <v>12</v>
       </c>
       <c r="D277" t="n">
-        <v>115.137</v>
+        <v>139.087</v>
       </c>
       <c r="E277" t="n">
         <v>49.5</v>
@@ -21770,28 +21770,28 @@
         <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>1</v>
+        <v>0.9999999999999439</v>
       </c>
       <c r="M277" t="n">
         <v>19.8</v>
       </c>
       <c r="N277" t="n">
-        <v>-3.364312195833777e-16</v>
+        <v>3.061524098208765e-14</v>
       </c>
       <c r="O277" t="n">
-        <v>133.957</v>
+        <v>157.907</v>
       </c>
       <c r="P277" t="n">
-        <v>159.9514058956916</v>
+        <v>120</v>
       </c>
       <c r="Q277" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
       <c r="S277" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T277" t="n">
         <v>0</v>
@@ -21823,7 +21823,7 @@
         <v>13</v>
       </c>
       <c r="D278" t="n">
-        <v>112.44</v>
+        <v>136.236</v>
       </c>
       <c r="E278" t="n">
         <v>56.911</v>
@@ -21841,25 +21841,25 @@
         <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>137.9636734693877</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M278" t="n">
         <v>22.7644</v>
       </c>
       <c r="N278" t="n">
-        <v>28.19081632653135</v>
+        <v>2.020202020202027</v>
       </c>
       <c r="O278" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P278" t="n">
-        <v>187.8603140589576</v>
+        <v>122</v>
       </c>
       <c r="Q278" t="n">
         <v>1</v>
@@ -21868,7 +21868,7 @@
         <v>0</v>
       </c>
       <c r="S278" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T278" t="n">
         <v>0</v>
@@ -21900,7 +21900,7 @@
         <v>14</v>
       </c>
       <c r="D279" t="n">
-        <v>112.44</v>
+        <v>136.236</v>
       </c>
       <c r="E279" t="n">
         <v>56.911</v>
@@ -21918,25 +21918,25 @@
         <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>137.9636734693877</v>
+        <v>162.245306122449</v>
       </c>
       <c r="M279" t="n">
         <v>22.7644</v>
       </c>
       <c r="N279" t="n">
-        <v>29.28163265306122</v>
+        <v>1.479591836734709</v>
       </c>
       <c r="O279" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P279" t="n">
-        <v>216.8491303854882</v>
+        <v>123.4647959183673</v>
       </c>
       <c r="Q279" t="n">
         <v>1</v>
@@ -21945,10 +21945,10 @@
         <v>0</v>
       </c>
       <c r="S279" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T279" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U279" t="n">
         <v>0</v>
@@ -21977,7 +21977,7 @@
         <v>15</v>
       </c>
       <c r="D280" t="n">
-        <v>114.258</v>
+        <v>122.799</v>
       </c>
       <c r="E280" t="n">
         <v>53.581</v>
@@ -21995,25 +21995,25 @@
         <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>138.4595918367347</v>
+        <v>147.1748979591837</v>
       </c>
       <c r="M280" t="n">
         <v>21.4324</v>
       </c>
       <c r="N280" t="n">
-        <v>129.4919121016346</v>
+        <v>177.4880666071144</v>
       </c>
       <c r="O280" t="n">
         <v>0</v>
       </c>
       <c r="P280" t="n">
-        <v>345.0461233661065</v>
+        <v>299.1779818594106</v>
       </c>
       <c r="Q280" t="n">
         <v>1</v>
@@ -22022,10 +22022,10 @@
         <v>0</v>
       </c>
       <c r="S280" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T280" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U280" t="n">
         <v>0</v>
@@ -22054,7 +22054,7 @@
         <v>16</v>
       </c>
       <c r="D281" t="n">
-        <v>131.363</v>
+        <v>140.444</v>
       </c>
       <c r="E281" t="n">
         <v>41.57</v>
@@ -22072,37 +22072,37 @@
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>151.0112244897959</v>
+        <v>160.2775510204082</v>
       </c>
       <c r="M281" t="n">
         <v>16.628</v>
       </c>
       <c r="N281" t="n">
-        <v>577.7663265306123</v>
+        <v>599.9999999999999</v>
       </c>
       <c r="O281" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>-1.4210854715202e-14</v>
       </c>
       <c r="P281" t="n">
-        <v>917.0347866314128</v>
+        <v>893.1779818594105</v>
       </c>
       <c r="Q281" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
       <c r="S281" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T281" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U281" t="n">
         <v>0</v>
@@ -22131,7 +22131,7 @@
         <v>17</v>
       </c>
       <c r="D282" t="n">
-        <v>131.363</v>
+        <v>140.444</v>
       </c>
       <c r="E282" t="n">
         <v>41.57</v>
@@ -22149,37 +22149,37 @@
         <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>105.7571428571457</v>
+        <v>160.2775510204081</v>
       </c>
       <c r="M282" t="n">
         <v>16.628</v>
       </c>
       <c r="N282" t="n">
-        <v>-2.590968965751477e-12</v>
+        <v>7.979591836734707</v>
       </c>
       <c r="O282" t="n">
-        <v>44.34899999999719</v>
+        <v>4.263256414560601e-14</v>
       </c>
       <c r="P282" t="n">
-        <v>872.2378169344433</v>
+        <v>901.0777777777778</v>
       </c>
       <c r="Q282" t="n">
-        <v>-5.366681072753721e-15</v>
+        <v>1</v>
       </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
       <c r="S282" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T282" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U282" t="n">
         <v>0</v>
@@ -22208,7 +22208,7 @@
         <v>18</v>
       </c>
       <c r="D283" t="n">
-        <v>94.574</v>
+        <v>122.803</v>
       </c>
       <c r="E283" t="n">
         <v>48.767</v>
@@ -22226,37 +22226,37 @@
         <v>0</v>
       </c>
       <c r="J283" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="K283" t="n">
         <v>0</v>
       </c>
       <c r="L283" t="n">
-        <v>93.73438568326026</v>
+        <v>108.714081632653</v>
       </c>
       <c r="M283" t="n">
         <v>19.5068</v>
       </c>
       <c r="N283" t="n">
-        <v>-7.177199351112123e-14</v>
+        <v>2.799107746933728e-13</v>
       </c>
       <c r="O283" t="n">
-        <v>22.22110203040495</v>
+        <v>35.77000000000008</v>
       </c>
       <c r="P283" t="n">
-        <v>849.7922593279736</v>
+        <v>864.9464646464648</v>
       </c>
       <c r="Q283" t="n">
-        <v>0</v>
+        <v>4.736951571734001e-16</v>
       </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
       <c r="S283" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T283" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U283" t="n">
         <v>0</v>
@@ -22285,7 +22285,7 @@
         <v>19</v>
       </c>
       <c r="D284" t="n">
-        <v>91.65600000000001</v>
+        <v>117.645</v>
       </c>
       <c r="E284" t="n">
         <v>43.091</v>
@@ -22309,31 +22309,31 @@
         <v>0</v>
       </c>
       <c r="L284" t="n">
-        <v>3.499999999999998</v>
+        <v>3.499999999999889</v>
       </c>
       <c r="M284" t="n">
         <v>17.2364</v>
       </c>
       <c r="N284" t="n">
-        <v>4.485749594445078e-16</v>
+        <v>-1.197695141716836e-13</v>
       </c>
       <c r="O284" t="n">
-        <v>105.4624</v>
+        <v>131.4514000000001</v>
       </c>
       <c r="P284" t="n">
-        <v>743.2645825602968</v>
+        <v>732.1672727272727</v>
       </c>
       <c r="Q284" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
       <c r="S284" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T284" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U284" t="n">
         <v>0</v>
@@ -22362,7 +22362,7 @@
         <v>20</v>
       </c>
       <c r="D285" t="n">
-        <v>91.65600000000001</v>
+        <v>117.645</v>
       </c>
       <c r="E285" t="n">
         <v>43.091</v>
@@ -22395,22 +22395,22 @@
         <v>0</v>
       </c>
       <c r="O285" t="n">
-        <v>104.9724</v>
+        <v>130.9614</v>
       </c>
       <c r="P285" t="n">
-        <v>637.2318552875696</v>
+        <v>599.8830303030303</v>
       </c>
       <c r="Q285" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
       <c r="S285" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T285" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U285" t="n">
         <v>0</v>
@@ -22439,7 +22439,7 @@
         <v>21</v>
       </c>
       <c r="D286" t="n">
-        <v>93.696</v>
+        <v>119.884</v>
       </c>
       <c r="E286" t="n">
         <v>44.625</v>
@@ -22472,22 +22472,22 @@
         <v>0</v>
       </c>
       <c r="O286" t="n">
-        <v>108.606</v>
+        <v>134.794</v>
       </c>
       <c r="P286" t="n">
-        <v>527.5288249845393</v>
+        <v>463.7274747474747</v>
       </c>
       <c r="Q286" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
       <c r="S286" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T286" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U286" t="n">
         <v>0</v>
@@ -22516,7 +22516,7 @@
         <v>22</v>
       </c>
       <c r="D287" t="n">
-        <v>98.786</v>
+        <v>110.043</v>
       </c>
       <c r="E287" t="n">
         <v>40.775</v>
@@ -22549,22 +22549,22 @@
         <v>0</v>
       </c>
       <c r="O287" t="n">
-        <v>111.176</v>
+        <v>122.433</v>
       </c>
       <c r="P287" t="n">
-        <v>415.2298350855494</v>
+        <v>340.0577777777777</v>
       </c>
       <c r="Q287" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R287" t="n">
         <v>0</v>
       </c>
       <c r="S287" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T287" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U287" t="n">
         <v>0</v>
@@ -22593,7 +22593,7 @@
         <v>23</v>
       </c>
       <c r="D288" t="n">
-        <v>98.786</v>
+        <v>110.043</v>
       </c>
       <c r="E288" t="n">
         <v>40.775</v>
@@ -22623,25 +22623,25 @@
         <v>16.31</v>
       </c>
       <c r="N288" t="n">
-        <v>-1.77635683940025e-15</v>
+        <v>0</v>
       </c>
       <c r="O288" t="n">
-        <v>105.296</v>
+        <v>116.553</v>
       </c>
       <c r="P288" t="n">
-        <v>308.8702391259534</v>
+        <v>222.3274747474747</v>
       </c>
       <c r="Q288" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
       <c r="S288" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T288" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U288" t="n">
         <v>0</v>
@@ -22670,7 +22670,7 @@
         <v>24</v>
       </c>
       <c r="D289" t="n">
-        <v>97.666</v>
+        <v>102.145</v>
       </c>
       <c r="E289" t="n">
         <v>34.648</v>
@@ -22700,13 +22700,13 @@
         <v>13.8592</v>
       </c>
       <c r="N289" t="n">
-        <v>0</v>
+        <v>-1.77635683940025e-15</v>
       </c>
       <c r="O289" t="n">
-        <v>96.82519999999997</v>
+        <v>101.3042</v>
       </c>
       <c r="P289" t="n">
-        <v>211.0670068027211</v>
+        <v>120</v>
       </c>
       <c r="Q289" t="n">
         <v>-0</v>
@@ -22935,7 +22935,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1.497576842982014</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -22952,7 +22952,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>313.8697843410398</v>
+        <v>319.8694782498246</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -22986,7 +22986,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>164.6544897959191</v>
+        <v>162.765508142651</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -23003,7 +23003,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>161.245306122449</v>
+        <v>157.7248979591837</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -23020,7 +23020,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>254.9515039383694</v>
+        <v>311.6629645662981</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -23037,7 +23037,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>715.2775510204083</v>
+        <v>746.7775510204078</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -23054,7 +23054,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>96.75714285714315</v>
+        <v>159.2571428571429</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -23071,7 +23071,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>88.73438568326014</v>
+        <v>103.714081632653</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
